--- a/results/metrics_modelling4_7-dim_reduction.xlsx
+++ b/results/metrics_modelling4_7-dim_reduction.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH29"/>
+  <dimension ref="A1:DH49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11908,6 +11908,7806 @@
       </c>
       <c r="DH29" t="n">
         <v>0.0006577597009422421</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Logit_splashing_smote_8-dim_vae</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 8, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.0702936787113344}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.008332336889711188, 'beta_warmup_steps': 1796, 'beta_start': 0.011858617338155039, 'beta_end': 0.1537765028941463}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8371913580246914</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7222222222222221</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.7349537037037037</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.8013468013468014</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.837465564738292</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.8786458333333335</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.7910271546635184</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.8053571428571429</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.6825396825396826</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.819047619047619</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.7445887445887446</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2.6652374267578125, 2.722731113433838, 2.4528985023498535, 2.161219358444214, 2.767550230026245, 2.662040948867798, 2.1729419231414795</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.514945643288748</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.662040948867798</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.2381917609313743</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>0.019994020462036133, 0.02100086212158203, 0.019977092742919922, 0.020000457763671875, 0.01800084114074707, 0.018997669219970703, 0.01800060272216797</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.01942450659615653</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.01997709274291992</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.001047638821344783</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7547169811320755, 0.7924528301886793, 0.7547169811320755, 0.7735849056603774, 0.6981132075471698, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>0.9451127819548872, 0.7873015873015873, 0.826625386996904, 0.7856037151702786, 0.7770897832817337, 0.7530959752321982, 0.6981424148606811</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.7961388063997529</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.7856037151702786</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.0708424861719487</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.7764300688828991</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.7547169811320755</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.07474172428658582</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>0.9565217391304348, 0.7868852459016394, 0.8135593220338982, 0.7796610169491526, 0.8125, 0.7037037037037037, 0.7761194029850745</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>0.9230769230769231, 0.711111111111111, 0.7659574468085106, 0.7234042553191489, 0.7142857142857143, 0.6923076923076923, 0.6153846153846154</t>
+        </is>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.7350753940419593</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.0875017942915107</v>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>0.939799331103679, 0.7489981785063753, 0.7897583844212044, 0.7515326361341508, 0.7633928571428572, 0.698005698005698, 0.695752009184845</t>
+        </is>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.7696055849284014</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.7515326361341508</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.07629157946993749</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.8041357758148434</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.7868852459016394</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.0708603839996821</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>0.9705882352941176, 0.9230769230769231, 0.96, 0.92, 0.8666666666666667, 0.95, 0.7878787878787878</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>0.9, 0.5925925925925926, 0.6428571428571429, 0.6071428571428571, 0.6521739130434783, 0.5454545454545454, 0.6</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.6486030072986594</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0.1076397313601946</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0.9111729447023565</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0.05955031222902852</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.6857142857142857, 0.7058823529411765, 0.6764705882352942, 0.7647058823529411, 0.5588235294117647, 0.7647058823529411</t>
+        </is>
+      </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
+          <t>0.9473684210526315, 0.8888888888888888, 0.9473684210526315, 0.8947368421052632, 0.7894736842105263, 0.9473684210526315, 0.631578947368421</t>
+        </is>
+      </c>
+      <c r="BK30" t="n">
+        <v>0.8638262322472849</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0.1082250282804004</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0.7284513805522208</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0.1085028239567396</v>
+      </c>
+      <c r="BQ30" t="inlineStr">
+        <is>
+          <t>0.9759398496240601, 0.9047619047619048, 0.9349845201238389, 0.8591331269349846, 0.8978328173374613, 0.8065015479876161, 0.8173374613003097</t>
+        </is>
+      </c>
+      <c r="BR30" t="n">
+        <v>0.8852130325814537</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0.8978328173374613</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0.05698712402930067</v>
+      </c>
+      <c r="BU30" t="inlineStr">
+        <is>
+          <t>0.7830188679245284, 0.786833855799373, 0.7962382445141066, 0.7899686520376176, 0.7429467084639498, 0.8181818181818182, 0.8056426332288401</t>
+        </is>
+      </c>
+      <c r="BV30" t="inlineStr">
+        <is>
+          <t>0.8078782646233542, 0.8049422336328627, 0.8242546610533551, 0.8114099149411462, 0.7630165821805996, 0.8492353294956612, 0.8135578657960305</t>
+        </is>
+      </c>
+      <c r="BW30" t="n">
+        <v>0.8106135502461441</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0.8114099149411462</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0.02388108012583711</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0.7889758257357476</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0.7899686520376176</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>0.0218542376268101</v>
+      </c>
+      <c r="CC30" t="inlineStr">
+        <is>
+          <t>0.810958904109589, 0.8172043010752689, 0.8219178082191781, 0.8194070080862533, 0.7771739130434783, 0.8406593406593407, 0.8393782383419689</t>
+        </is>
+      </c>
+      <c r="CD30" t="inlineStr">
+        <is>
+          <t>0.7453874538745386, 0.744360902255639, 0.761904761904762, 0.749063670411985, 0.6962962962962963, 0.7883211678832117, 0.753968253968254</t>
+        </is>
+      </c>
+      <c r="CE30" t="n">
+        <v>0.7484717866563838</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0.749063670411985</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0.02548857940629277</v>
+      </c>
+      <c r="CH30" t="inlineStr">
+        <is>
+          <t>0.7781731789920638, 0.780782601665454, 0.7919112850619701, 0.7842353392491191, 0.7367351046698873, 0.8144902542712762, 0.7966732461551114</t>
+        </is>
+      </c>
+      <c r="CI30" t="n">
+        <v>0.7832858585806974</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>0.7842353392491191</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0.02212824448988821</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0.8180999305050111</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>0.8194070080862533</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>0.0196567448557797</v>
+      </c>
+      <c r="CO30" t="inlineStr">
+        <is>
+          <t>0.925, 0.9101796407185628, 0.9433962264150944, 0.9212121212121213, 0.8827160493827161, 0.9683544303797469, 0.9</t>
+        </is>
+      </c>
+      <c r="CP30" t="inlineStr">
+        <is>
+          <t>0.6392405063291139, 0.6513157894736842, 0.65, 0.6493506493506493, 0.5987261146496815, 0.6708074534161491, 0.6834532374100719</t>
+        </is>
+      </c>
+      <c r="CQ30" t="n">
+        <v>0.6489848215184786</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>0.02476110452362955</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>0.9215512097297489</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>0.9212121212121213</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>0.02613616064906989</v>
+      </c>
+      <c r="CW30" t="inlineStr">
+        <is>
+          <t>0.7219512195121951, 0.7414634146341463, 0.7281553398058253, 0.7378640776699029, 0.6941747572815534, 0.7427184466019418, 0.7864077669902912</t>
+        </is>
+      </c>
+      <c r="CX30" t="inlineStr">
+        <is>
+          <t>0.8938053097345132, 0.868421052631579, 0.9203539823008849, 0.8849557522123894, 0.831858407079646, 0.9557522123893806, 0.8407079646017699</t>
+        </is>
+      </c>
+      <c r="CY30" t="n">
+        <v>0.8851220972785947</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>0.8849557522123894</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>0.04034473854768639</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>0.7361050032136938</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>0.7378640776699029</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>0.02571154509499585</v>
+      </c>
+      <c r="DE30" t="inlineStr">
+        <is>
+          <t>0.9076840060436002, 0.8866923406076166, 0.9123850846292637, 0.9108815190308446, 0.8697697396683564, 0.9197955150786151, 0.8971775925766818</t>
+        </is>
+      </c>
+      <c r="DF30" t="n">
+        <v>0.9006265425192826</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>0.9076840060436002</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>0.01611957406821628</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_smote_8-dim_vae</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 8, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.0702936787113344}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.008332336889711188, 'beta_warmup_steps': 1796, 'beta_start': 0.011858617338155039, 'beta_end': 0.1537765028941463}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9467592592592592</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.8680555555555556</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.9997767857142857</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>4.432888746261597, 4.222791910171509, 4.030780553817749, 3.895732879638672, 4.5095131397247314, 4.3703436851501465, 3.8952724933624268</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>4.193903344018119</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.222791910171509</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.2370606807004072</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>0.01903057098388672, 0.020195484161376953, 0.01999950408935547, 0.018999099731445312, 0.01900005340576172, 0.01899886131286621, 0.01899862289428711</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.01931745665413993</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.01900005340576172</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.0004962255111420642</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8113207547169812, 0.8679245283018868, 0.8867924528301887, 0.9056603773584906, 0.8301886792452831, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8166666666666667, 0.8738390092879257, 0.8769349845201238, 0.891640866873065, 0.8560371517027863, 0.8359133126934984</t>
+        </is>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.8712000589709568</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.8738390092879257</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.03911203420142195</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.8734151941699111</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.04718541712559663</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8484848484848486, 0.8923076923076922, 0.9117647058823528, 0.9275362318840579, 0.8524590163934426, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7499999999999999, 0.8292682926829269, 0.8421052631578947, 0.8648648648648649, 0.7999999999999999, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.831450935622951</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.05780238283540751</v>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.7992424242424243, 0.8607879924953096, 0.8769349845201238, 0.8962005483744614, 0.8262295081967213, 0.8359133126934984</t>
+        </is>
+      </c>
+      <c r="AU31" t="n">
+        <v>0.8648060148365532</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.8607879924953096</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.0485765257294913</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.8981610940501553</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.8923076923076922</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.04030876715803101</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9032258064516129, 0.9354838709677419, 0.9117647058823529, 0.9142857142857143, 0.9629629629629629, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>1.0, 0.6818181818181818, 0.7727272727272727, 0.8421052631578947, 0.8888888888888888, 0.6923076923076923, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.8096172833014939</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0.1038170251993076</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0.9222888496675429</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0.0254143785675352</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.8529411764705882, 0.9117647058823529, 0.9411764705882353, 0.7647058823529411, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.8947368421052632, 0.8421052631578947, 0.8421052631578947, 0.9473684210526315, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK31" t="n">
+        <v>0.8634085213032582</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0.04824154525042645</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0.8789915966386553</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0.07519012927148752</v>
+      </c>
+      <c r="BQ31" t="inlineStr">
+        <is>
+          <t>0.9969924812030075, 0.9444444444444444, 0.9752321981424149, 0.9674922600619195, 0.956656346749226, 0.9458204334365325, 0.9009287925696595</t>
+        </is>
+      </c>
+      <c r="BR31" t="n">
+        <v>0.9553667080867434</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0.9566563467492259</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0.02790276153736005</v>
+      </c>
+      <c r="BU31" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 0.987460815047022, 0.9905956112852664, 0.9968652037617555, 0.9905956112852664, 0.9937304075235109, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV31" t="inlineStr">
+        <is>
+          <t>0.9931361968486941, 0.9882969619169876, 0.9907208523068992, 0.995575221238938, 0.9887232580118567, 0.9931480367729186, 0.9931480367729186</t>
+        </is>
+      </c>
+      <c r="BW31" t="n">
+        <v>0.9918212234098875</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>0.9931361968486941</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0.002466088501712329</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>0.9923841068928904</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0.9937106918238994</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>0.002830985269677727</v>
+      </c>
+      <c r="CC31" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 0.9901960784313727, 0.9927007299270073, 0.9975786924939467, 0.9927360774818401, 0.9951456310679612, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CD31" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9826086956521738, 0.9867841409691629, 0.9955555555555555, 0.9866666666666667, 0.9911504424778761, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CE31" t="n">
+        <v>0.9892951980395981</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0.00391775757602278</v>
+      </c>
+      <c r="CH31" t="inlineStr">
+        <is>
+          <t>0.9931361968486941, 0.9864023870417733, 0.989742435448085, 0.9965671240247511, 0.9897013720742533, 0.9931480367729186, 0.9931480367729186</t>
+        </is>
+      </c>
+      <c r="CI31" t="n">
+        <v>0.9916922269976277</v>
+      </c>
+      <c r="CJ31" t="n">
+        <v>0.9931361968486941</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>0.003066781265912342</v>
+      </c>
+      <c r="CL31" t="n">
+        <v>0.9940892559556574</v>
+      </c>
+      <c r="CM31" t="n">
+        <v>0.9951219512195122</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>0.002216509848786183</v>
+      </c>
+      <c r="CO31" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 0.9950738916256158, 0.9951219512195122, 0.9951690821256038, 0.9903381642512077, 0.9951456310679612, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CP31" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9741379310344828, 0.9824561403508771, 1.0, 0.9910714285714286, 0.9911504424778761, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CQ31" t="n">
+        <v>0.988730975341488</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>0.007581562202884888</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>0.994445186082482</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>0.9951219512195122</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>0.001676910122838312</v>
+      </c>
+      <c r="CW31" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 0.9853658536585366, 0.9902912621359223, 1.0, 0.9951456310679612, 0.9951456310679612, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CX31" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9912280701754386, 0.9911504424778761, 0.9911504424778761, 0.9823008849557522, 0.9911504424778761, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY31" t="n">
+        <v>0.9898973096457959</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA31" t="n">
+        <v>0.003101343053142972</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>0.9937451371739793</v>
+      </c>
+      <c r="DC31" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>0.00429359523576749</v>
+      </c>
+      <c r="DE31" t="inlineStr">
+        <is>
+          <t>0.9997625728469673, 0.9997432605905007, 0.9998926024572558, 0.9995918893375719, 0.9993341352349858, 0.9998281639316092, 0.9996348483546696</t>
+        </is>
+      </c>
+      <c r="DF31" t="n">
+        <v>0.9996839246790801</v>
+      </c>
+      <c r="DG31" t="n">
+        <v>0.9997432605905007</v>
+      </c>
+      <c r="DH31" t="n">
+        <v>0.0001720835788108993</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Logit_no_fragmentation_smote_8-dim_vae</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 8, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.0702936787113344}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.008332336889711188, 'beta_warmup_steps': 1796, 'beta_start': 0.011858617338155039, 'beta_end': 0.1537765028941463}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9372727272727273</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.9777777777777777</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.603448275862069</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.8860759493670886</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.717948717948718</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.9030310068517012</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.790052053209948</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.837533387527581</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.9502762430939227</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.7889908256880734</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.862155388471178</v>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2.9493439197540283, 3.132455587387085, 2.3921115398406982, 2.866551160812378, 2.854830265045166, 2.8606176376342773, 3.384286642074585</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.920028107506888</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.866551160812378</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.2805242252872984</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>0.01699972152709961, 0.01699995994567871, 0.017000436782836914, 0.015999794006347656, 0.016999483108520508, 0.01700758934020996, 0.018000125885009766</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.01700101579938616</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.01699995994567871</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.0005346179848209727</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7735849056603774, 0.8301886792452831, 0.7924528301886793, 0.7924528301886793, 0.8490566037735849, 0.7735849056603774</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>0.8769230769230769, 0.7774725274725275, 0.8388278388278387, 0.8131868131868132, 0.8131868131868132, 0.8287545787545787, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.8277864992150705</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.8287545787545787</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.02886522494436219</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.809024658081262</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.03150021327981726</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>0.7777777777777778, 0.6470588235294117, 0.7272727272727273, 0.6857142857142857, 0.6857142857142857, 0.7333333333333334, 0.7000000000000001</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8333333333333333, 0.8767123287671232, 0.8450704225352113, 0.8450704225352113, 0.8947368421052632, 0.8181818181818181</t>
+        </is>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.8574277223352641</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.8450704225352113</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.02720256751288998</v>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>0.8333333333333333, 0.7401960784313725, 0.8019925280199253, 0.7653923541247485, 0.7653923541247485, 0.8140350877192983, 0.759090909090909</t>
+        </is>
+      </c>
+      <c r="AU32" t="n">
+        <v>0.7827760921206194</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0.7653923541247485</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0.03135252327028514</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.7081244619059746</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.03901131473709673</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.55, 0.631578947368421, 0.5714285714285714, 0.5714285714285714, 0.6875, 0.5384615384615384</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>0.9696969696969697, 0.9090909090909091, 0.9411764705882353, 0.9375, 0.9375, 0.918918918918919, 1.0</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>0.9448404668992906</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0.02861459950539583</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0.6024377564791098</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0.05474089757931979</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>0.8205128205128205, 0.7692307692307693, 0.8205128205128205, 0.7692307692307693, 0.7692307692307693, 0.8717948717948718, 0.6923076923076923</t>
+        </is>
+      </c>
+      <c r="BK32" t="n">
+        <v>0.7875457875457876</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0.05257399301980704</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0.8680272108843538</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0.07130212325580343</v>
+      </c>
+      <c r="BQ32" t="inlineStr">
+        <is>
+          <t>0.9128205128205129, 0.9304029304029303, 0.9322344322344323, 0.8956043956043955, 0.9395604395604396, 0.924908424908425, 0.9633699633699634</t>
+        </is>
+      </c>
+      <c r="BR32" t="n">
+        <v>0.9284144427001569</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0.9304029304029303</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0.01962734999566395</v>
+      </c>
+      <c r="BU32" t="inlineStr">
+        <is>
+          <t>0.7830188679245284, 0.896551724137931, 0.8119122257053292, 0.8025078369905956, 0.8150470219435737, 0.8369905956112853, 0.8244514106583072</t>
+        </is>
+      </c>
+      <c r="BV32" t="inlineStr">
+        <is>
+          <t>0.8144078144078144, 0.8995223730517848, 0.8268476621417797, 0.8316742081447964, 0.8477124183006536, 0.8701608848667672, 0.865359477124183</t>
+        </is>
+      </c>
+      <c r="BW32" t="n">
+        <v>0.8508121197196827</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0.8477124183006536</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0.02734469282649352</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0.8243542404245073</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0.8150470219435737</v>
+      </c>
+      <c r="CB32" t="n">
+        <v>0.03337978425386958</v>
+      </c>
+      <c r="CC32" t="inlineStr">
+        <is>
+          <t>0.6820276497695852, 0.823529411764706, 0.7087378640776698, 0.7069767441860465, 0.7255813953488371, 0.7547169811320755, 0.7431192660550459</t>
+        </is>
+      </c>
+      <c r="CD32" t="inlineStr">
+        <is>
+          <t>0.8353221957040572, 0.926829268292683, 0.8611111111111112, 0.8510638297872339, 0.8605200945626477, 0.8779342723004696, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="CE32" t="n">
+        <v>0.8684924912035529</v>
+      </c>
+      <c r="CF32" t="n">
+        <v>0.8611111111111112</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0.02677347047579003</v>
+      </c>
+      <c r="CH32" t="inlineStr">
+        <is>
+          <t>0.7586749227368212, 0.8751793400286945, 0.7849244875943905, 0.7790202869866403, 0.7930507449557425, 0.8163256267162726, 0.8048929663608563</t>
+        </is>
+      </c>
+      <c r="CI32" t="n">
+        <v>0.8017240536256312</v>
+      </c>
+      <c r="CJ32" t="n">
+        <v>0.7930507449557425</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>0.03452756132466952</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>0.7349556160477094</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>0.7255813953488371</v>
+      </c>
+      <c r="CN32" t="n">
+        <v>0.042530505751283</v>
+      </c>
+      <c r="CO32" t="inlineStr">
+        <is>
+          <t>0.556390977443609, 0.7549019607843137, 0.6033057851239669, 0.5846153846153846, 0.6, 0.6299212598425197, 0.6090225563909775</t>
+        </is>
+      </c>
+      <c r="CP32" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9631336405529954, 0.9393939393939394, 0.9523809523809523, 0.9629629629629629, 0.9739583333333334, 0.978494623655914</t>
+        </is>
+      </c>
+      <c r="CQ32" t="n">
+        <v>0.9594671997465776</v>
+      </c>
+      <c r="CR32" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>0.01327550886385209</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>0.619736846314396</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>0.6033057851239669</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>0.05903251586600707</v>
+      </c>
+      <c r="CW32" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.9058823529411765, 0.8588235294117647, 0.8941176470588236, 0.9176470588235294, 0.9411764705882353, 0.9529411764705882</t>
+        </is>
+      </c>
+      <c r="CX32" t="inlineStr">
+        <is>
+          <t>0.7478632478632479, 0.8931623931623932, 0.7948717948717948, 0.7692307692307693, 0.7777777777777778, 0.7991452991452992, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="CY32" t="n">
+        <v>0.7942612942612942</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>0.04330683235889671</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>0.9073629451780713</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>0.9058823529411765</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>0.03060745829552021</v>
+      </c>
+      <c r="DE32" t="inlineStr">
+        <is>
+          <t>0.9141229141229141, 0.9549019607843138, 0.9068878833584716, 0.9240321769733535, 0.9275012569130217, 0.9452991452991454, 0.9256913021618904</t>
+        </is>
+      </c>
+      <c r="DF32" t="n">
+        <v>0.9283480913733015</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>0.9256913021618904</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>0.01549997778967688</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smote_8-dim_vae</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 8, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.0702936787113344}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.008332336889711188, 'beta_warmup_steps': 1796, 'beta_start': 0.011858617338155039, 'beta_end': 0.1537765028941463}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.7804878048780488</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9590909090909091</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8489594987692997</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.8545454545454545</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.9865319865319865</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.9998258042039252</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.9828917050691244</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.9867901521309952</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.9953703703703703</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.9862385321100917</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.9907834101382489</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>4.6689043045043945, 4.854514122009277, 4.053288698196411, 4.669302463531494, 4.656439304351807, 4.587846040725708, 5.13029146194458</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.660083770751953</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4.668904304504395</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.3005929978063268</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>0.017000913619995117, 0.017000675201416016, 0.018438339233398438, 0.01700139045715332, 0.017000675201416016, 0.018001556396484375, 0.01599907875061035</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.01720608983721052</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.01700091361999512</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.0007345038019942437</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.8113207547169812, 0.9245283018867925, 0.8679245283018868, 0.9433962264150944, 0.9433962264150944, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>0.7897435897435897, 0.7802197802197802, 0.88003663003663, 0.8415750915750916, 0.8928571428571428, 0.9157509157509157, 0.8516483516483516</t>
+        </is>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.850261643118786</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.8516483516483516</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.04726135200707567</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.8792053509034642</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.05356674119130207</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>0.6875, 0.6666666666666666, 0.8461538461538461, 0.7586206896551724, 0.88, 0.888888888888889, 0.75</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>0.868421052631579, 0.868421052631579, 0.9500000000000001, 0.9090909090909091, 0.962962962962963, 0.9620253164556962, 0.8918918918918919</t>
+        </is>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.9161161693806598</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.03898022219563746</v>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>0.7779605263157895, 0.7675438596491229, 0.8980769230769231, 0.8338557993730407, 0.9214814814814816, 0.9254571026722926, 0.8209459459459459</t>
+        </is>
+      </c>
+      <c r="AU33" t="n">
+        <v>0.8493316626449422</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0.8338557993730407</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.06118486562215546</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.782547155909225</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0.08361943965463597</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>0.6470588235294118, 0.625, 0.9166666666666666, 0.7333333333333333, 1.0, 0.9230769230769231, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.8918918918918919, 0.926829268292683, 0.9210526315789473, 0.9285714285714286, 0.95, 0.9428571428571428</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>0.9218706078691409</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0.02104180387512617</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0.787400344753286</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0.1433706518091539</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7142857142857143, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.8461538461538461, 0.9743589743589743, 0.8974358974358975, 1.0, 0.9743589743589743, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="BK33" t="n">
+        <v>0.9120879120879121</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0.06407639444884945</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0.7884353741496597</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0.05070651742471896</v>
+      </c>
+      <c r="BQ33" t="inlineStr">
+        <is>
+          <t>0.9264957264957264, 0.9120879120879121, 0.967032967032967, 0.9413919413919414, 0.967032967032967, 0.956043956043956, 0.9578754578754579</t>
+        </is>
+      </c>
+      <c r="BR33" t="n">
+        <v>0.9468515611372755</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0.956043956043956</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0.01954220143401315</v>
+      </c>
+      <c r="BU33" t="inlineStr">
+        <is>
+          <t>0.9874213836477987, 0.9937304075235109, 0.987460815047022, 0.9780564263322884, 0.9843260188087775, 0.9968652037617555, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV33" t="inlineStr">
+        <is>
+          <t>0.9838217338217339, 0.9919808949220714, 0.9877073906485672, 0.9775515334338863, 0.9818250377073907, 0.9978632478632479, 0.9919808949220714</t>
+        </is>
+      </c>
+      <c r="BW33" t="n">
+        <v>0.9875329619027099</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0.9877073906485672</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0.006461932223968072</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0.988798666092095</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0.987460815047022</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>0.006009518856388799</v>
+      </c>
+      <c r="CC33" t="inlineStr">
+        <is>
+          <t>0.9761904761904762, 0.9882352941176471, 0.9767441860465116, 0.9595375722543352, 0.9707602339181286, 0.9941520467836257, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CD33" t="inlineStr">
+        <is>
+          <t>0.9914529914529915, 0.9957264957264957, 0.9914163090128757, 0.9849462365591398, 0.9892933618843683, 0.9978586723768736, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CE33" t="n">
+        <v>0.9923457946770343</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0.9914529914529915</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0.004122792867456019</v>
+      </c>
+      <c r="CH33" t="inlineStr">
+        <is>
+          <t>0.9838217338217339, 0.9919808949220714, 0.9840802475296937, 0.9722419044067375, 0.9800267979012485, 0.9960053595802496, 0.9919808949220714</t>
+        </is>
+      </c>
+      <c r="CI33" t="n">
+        <v>0.9857339761548294</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>0.9840802475296937</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0.007602148929470253</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0.9791221576326244</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>0.9767441860465116</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0.0110823111222333</v>
+      </c>
+      <c r="CO33" t="inlineStr">
+        <is>
+          <t>0.9761904761904762, 0.9882352941176471, 0.9655172413793104, 0.9431818181818182, 0.9651162790697675, 0.9883720930232558, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CP33" t="inlineStr">
+        <is>
+          <t>0.9914529914529915, 0.9957264957264957, 0.9956896551724138, 0.9913419913419913, 0.9914163090128756, 1.0, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CQ33" t="n">
+        <v>0.9944791340618948</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>0.9956896551724138</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>0.003010392597214278</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>0.9735497851542746</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>0.9761904761904762</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>0.01565640721946706</v>
+      </c>
+      <c r="CW33" t="inlineStr">
+        <is>
+          <t>0.9761904761904762, 0.9882352941176471, 0.9882352941176471, 0.9764705882352941, 0.9764705882352941, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CX33" t="inlineStr">
+        <is>
+          <t>0.9914529914529915, 0.9957264957264957, 0.9871794871794872, 0.9786324786324786, 0.9871794871794872, 0.9957264957264957, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CY33" t="n">
+        <v>0.9902319902319903</v>
+      </c>
+      <c r="CZ33" t="n">
+        <v>0.9914529914529915</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>0.005919023024928373</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>0.9848339335734294</v>
+      </c>
+      <c r="DC33" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>0.008274899891765483</v>
+      </c>
+      <c r="DE33" t="inlineStr">
+        <is>
+          <t>0.9994912494912495, 0.9997486173956762, 0.9992961287078934, 0.9984917043740573, 0.9984917043740572, 0.9999497234791352, 0.9994469582704877</t>
+        </is>
+      </c>
+      <c r="DF33" t="n">
+        <v>0.9992737265846509</v>
+      </c>
+      <c r="DG33" t="n">
+        <v>0.9994469582704877</v>
+      </c>
+      <c r="DH33" t="n">
+        <v>0.0005323046719516647</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Logit_splashing_smote_9-dim_vae</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 9, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.0790071604095478}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.008367466805612848, 'beta_warmup_steps': 1817, 'beta_start': 0.005364676165587271, 'beta_end': 0.06463895620675993}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.7826086956521738</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8387345679012346</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.7188905547226387</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.7268518518518519</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.6551724137931035</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.8215488215488216</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.9316770186335404</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.8498583569405099</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.9013144841269841</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.8149706722461886</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.8382440476190476</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.6911764705882353</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.8952380952380953</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.7800829875518672</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>3.0675156116485596, 2.7735345363616943, 3.430464267730713, 3.1155052185058594, 3.6389970779418945, 3.3699562549591064, 3.7225964069366455</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.302652767726353</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.369956254959106</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.3118208011398902</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>0.01900005340576172, 0.018999099731445312, 0.017992734909057617, 0.01999974250793457, 0.01900005340576172, 0.02099919319152832, 0.01900029182434082</t>
+        </is>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.01928445271083287</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.01900005340576172</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.0008819174686932168</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7547169811320755, 0.6981132075471698, 0.7169811320754716, 0.7735849056603774, 0.6792452830188679, 0.6792452830188679</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7738095238095238, 0.7530959752321982, 0.7329721362229102, 0.7770897832817337, 0.7151702786377709, 0.6571207430340558</t>
+        </is>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.7611507760999137</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.7530959752321982</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.07470130508683993</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.7468303883398223</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.7169811320754716</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.08040349037607583</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.7936507936507937, 0.7037037037037037, 0.7540983606557378, 0.8125, 0.7017543859649124, 0.746268656716418</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.6976744186046512, 0.6923076923076923, 0.6666666666666666, 0.7142857142857143, 0.653061224489796, 0.5641025641025641</t>
+        </is>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.6975478746517639</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.0925291318158655</v>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7456626061277225, 0.698005698005698, 0.7103825136612022, 0.7633928571428572, 0.6774078052273542, 0.6551856104094911</t>
+        </is>
+      </c>
+      <c r="AU34" t="n">
+        <v>0.7384048690079326</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0.7103825136612022</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0.08131229455333587</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0.7792618633641012</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0.7540983606557378</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0.07700967342922466</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8928571428571429, 0.95, 0.8518518518518519, 0.8666666666666667, 0.8695652173913043, 0.7575757575757576</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.6, 0.5454545454545454, 0.5769230769230769, 0.6521739130434783, 0.5333333333333333, 0.55</t>
+        </is>
+      </c>
+      <c r="BC34" t="n">
+        <v>0.6218031015513852</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0.1175442117857569</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0.8759105398856953</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0.05972070302142789</v>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.7142857142857143, 0.5588235294117647, 0.6764705882352942, 0.7647058823529411, 0.5882352941176471, 0.7352941176470589</t>
+        </is>
+      </c>
+      <c r="BJ34" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.9473684210526315, 0.7894736842105263, 0.7894736842105263, 0.8421052631578947, 0.5789473684210527</t>
+        </is>
+      </c>
+      <c r="BK34" t="n">
+        <v>0.8107769423558897</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0.1081330927559129</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0.7115246098439376</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>0.1175112526789746</v>
+      </c>
+      <c r="BQ34" t="inlineStr">
+        <is>
+          <t>0.9624060150375939, 0.8587301587301587, 0.9195046439628484, 0.8436532507739938, 0.913312693498452, 0.868421052631579, 0.8343653250773995</t>
+        </is>
+      </c>
+      <c r="BR34" t="n">
+        <v>0.8857704485302893</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>0.868421052631579</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>0.04345458241139143</v>
+      </c>
+      <c r="BU34" t="inlineStr">
+        <is>
+          <t>0.7515723270440252, 0.774294670846395, 0.7523510971786834, 0.786833855799373, 0.7962382445141066, 0.8087774294670846, 0.8087774294670846</t>
+        </is>
+      </c>
+      <c r="BV34" t="inlineStr">
+        <is>
+          <t>0.7636304770127347, 0.7796106118955927, 0.7902740785290833, 0.798994758999914, 0.8062763123979724, 0.8299682103273477, 0.8179826445570926</t>
+        </is>
+      </c>
+      <c r="BW34" t="n">
+        <v>0.7981052991028197</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>0.798994758999914</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>0.02094143329758172</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>0.7826921506166791</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>0.786833855799373</v>
+      </c>
+      <c r="CB34" t="n">
+        <v>0.02242789887782578</v>
+      </c>
+      <c r="CC34" t="inlineStr">
+        <is>
+          <t>0.7893333333333333, 0.8125, 0.7749287749287749, 0.8210526315789473, 0.8302872062663185, 0.836461126005362, 0.8415584415584415</t>
+        </is>
+      </c>
+      <c r="CD34" t="inlineStr">
+        <is>
+          <t>0.6973180076628352, 0.7165354330708662, 0.7247386759581881, 0.7364341085271319, 0.7450980392156863, 0.7698113207547168, 0.758893280632411</t>
+        </is>
+      </c>
+      <c r="CE34" t="n">
+        <v>0.7355469808316908</v>
+      </c>
+      <c r="CF34" t="n">
+        <v>0.7364341085271319</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0.02314802431740455</v>
+      </c>
+      <c r="CH34" t="inlineStr">
+        <is>
+          <t>0.7433256704980843, 0.7645177165354331, 0.7498337254434815, 0.7787433700530395, 0.7876926227410024, 0.8031362233800394, 0.8002258610954263</t>
+        </is>
+      </c>
+      <c r="CI34" t="n">
+        <v>0.7753535985352152</v>
+      </c>
+      <c r="CJ34" t="n">
+        <v>0.7787433700530395</v>
+      </c>
+      <c r="CK34" t="n">
+        <v>0.02187207676177031</v>
+      </c>
+      <c r="CL34" t="n">
+        <v>0.8151602162387396</v>
+      </c>
+      <c r="CM34" t="n">
+        <v>0.8210526315789473</v>
+      </c>
+      <c r="CN34" t="n">
+        <v>0.02301184460128269</v>
+      </c>
+      <c r="CO34" t="inlineStr">
+        <is>
+          <t>0.8705882352941177, 0.8715083798882681, 0.9379310344827586, 0.896551724137931, 0.8983050847457628, 0.9341317365269461, 0.9050279329608939</t>
+        </is>
+      </c>
+      <c r="CP34" t="inlineStr">
+        <is>
+          <t>0.6148648648648649, 0.65, 0.5977011494252874, 0.6551724137931034, 0.6690140845070423, 0.6710526315789473, 0.6857142857142857</t>
+        </is>
+      </c>
+      <c r="CQ34" t="n">
+        <v>0.6490742042690758</v>
+      </c>
+      <c r="CR34" t="n">
+        <v>0.6551724137931034</v>
+      </c>
+      <c r="CS34" t="n">
+        <v>0.02944889176382193</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>0.9020063040052397</v>
+      </c>
+      <c r="CU34" t="n">
+        <v>0.8983050847457628</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>0.02476296139298036</v>
+      </c>
+      <c r="CW34" t="inlineStr">
+        <is>
+          <t>0.7219512195121951, 0.7609756097560976, 0.6601941747572816, 0.7572815533980582, 0.7718446601941747, 0.7572815533980582, 0.7864077669902912</t>
+        </is>
+      </c>
+      <c r="CX34" t="inlineStr">
+        <is>
+          <t>0.8053097345132744, 0.7982456140350878, 0.9203539823008849, 0.8407079646017699, 0.8407079646017699, 0.9026548672566371, 0.8495575221238938</t>
+        </is>
+      </c>
+      <c r="CY34" t="n">
+        <v>0.8510768070619026</v>
+      </c>
+      <c r="CZ34" t="n">
+        <v>0.8407079646017699</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>0.04236359151694371</v>
+      </c>
+      <c r="DB34" t="n">
+        <v>0.7451337911437367</v>
+      </c>
+      <c r="DC34" t="n">
+        <v>0.7572815533980582</v>
+      </c>
+      <c r="DD34" t="n">
+        <v>0.03912485716900138</v>
+      </c>
+      <c r="DE34" t="inlineStr">
+        <is>
+          <t>0.8781567019210016, 0.8979460847240052, 0.8951585187730904, 0.9086476501417649, 0.8970487155253887, 0.9163158346937021, 0.9029770598848698</t>
+        </is>
+      </c>
+      <c r="DF34" t="n">
+        <v>0.8994643665234033</v>
+      </c>
+      <c r="DG34" t="n">
+        <v>0.8979460847240052</v>
+      </c>
+      <c r="DH34" t="n">
+        <v>0.01109273338197748</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_smote_9-dim_vae</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 9, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.0790071604095478}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.008367466805612848, 'beta_warmup_steps': 1817, 'beta_start': 0.005364676165587271, 'beta_end': 0.06463895620675993}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9398148148148148</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.8680555555555556</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.9932659932659933</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.9896907216494846</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.9998759920634921</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.9926016341171782</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.9809523809523809</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.9903846153846153</v>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>5.091884136199951, 4.7600438594818115, 5.378701210021973, 5.064801931381226, 5.5119969844818115, 5.284348011016846, 5.671129941940308</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>5.251843724931989</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>5.284348011016846</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.2836166453365245</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>0.019000530242919922, 0.017998695373535156, 0.018000125885009766, 0.019001245498657227, 0.02000117301940918, 0.020931005477905273, 0.018999814987182617</t>
+        </is>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.01913322721208845</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.01900053024291992</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.0009716880898481078</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.7924528301886793, 0.9056603773584906, 0.9622641509433962, 0.9056603773584906, 0.8867924528301887, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8023809523809524, 0.914860681114551, 0.9705882352941176, 0.891640866873065, 0.8885448916408669, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.8989027189823297</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.891640866873065</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.05028695648832867</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.9003693720674855</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.05321057390929988</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8307692307692307, 0.923076923076923, 0.9696969696969697, 0.9275362318840579, 0.9090909090909091, 0.9117647058823528</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7317073170731708, 0.8780487804878049, 0.9500000000000001, 0.8648648648648649, 0.8500000000000001, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.8658815242897401</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.8648648648648649</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.06784159847783842</v>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.7812382739212007, 0.900562851782364, 0.959848484848485, 0.8962005483744614, 0.8795454545454546, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AU35" t="n">
+        <v>0.8932377044750605</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0.8962005483744614</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0.0557212475707802</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0.9205938846603807</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0.04376838577880027</v>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9, 0.967741935483871, 1.0, 0.9142857142857143, 0.9375, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>1.0, 0.6521739130434783, 0.8181818181818182, 0.9047619047619048, 0.8888888888888888, 0.8095238095238095, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BC35" t="n">
+        <v>0.8450907996511133</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0.0990603830252184</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0.9396054716568407</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0.03266406066304685</v>
+      </c>
+      <c r="BI35" t="inlineStr">
+        <is>
+          <t>1.0, 0.7714285714285715, 0.8823529411764706, 0.9411764705882353, 0.9411764705882353, 0.8823529411764706, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ35" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.9473684210526315, 1.0, 0.8421052631578947, 0.8947368421052632, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK35" t="n">
+        <v>0.893483709273183</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0.05750773887510659</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0.9043217286914766</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0.06606503290337368</v>
+      </c>
+      <c r="BQ35" t="inlineStr">
+        <is>
+          <t>0.9789473684210526, 0.9222222222222223, 0.9736842105263157, 0.9798761609907121, 0.9256965944272446, 0.9256965944272446, 0.9148606811145511</t>
+        </is>
+      </c>
+      <c r="BR35" t="n">
+        <v>0.9458548331613347</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0.9256965944272446</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>0.02766867186737657</v>
+      </c>
+      <c r="BU35" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9905956112852664, 0.9905956112852664, 0.9968652037617555, 1.0, 0.9905956112852664</t>
+        </is>
+      </c>
+      <c r="BV35" t="inlineStr">
+        <is>
+          <t>0.9931361968486941, 1.0, 0.9907208523068992, 0.9887232580118567, 0.995575221238938, 1.0, 0.9907208523068992</t>
+        </is>
+      </c>
+      <c r="BW35" t="n">
+        <v>0.9941251972447553</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>0.9931361968486941</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0.004216758785420018</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0.9946232470630649</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0.9937106918238994</v>
+      </c>
+      <c r="CB35" t="n">
+        <v>0.004006131391269777</v>
+      </c>
+      <c r="CC35" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 0.9927007299270073, 0.9927360774818401, 0.9975786924939467, 1.0, 0.9927007299270073</t>
+        </is>
+      </c>
+      <c r="CD35" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9867841409691629, 0.9866666666666667, 0.9955555555555555, 1.0, 0.9867841409691629</t>
+        </is>
+      </c>
+      <c r="CE35" t="n">
+        <v>0.9924201352340606</v>
+      </c>
+      <c r="CF35" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="CG35" t="n">
+        <v>0.005643997358652304</v>
+      </c>
+      <c r="CH35" t="inlineStr">
+        <is>
+          <t>0.9931361968486941, 1.0, 0.989742435448085, 0.9897013720742533, 0.9965671240247511, 1.0, 0.989742435448085</t>
+        </is>
+      </c>
+      <c r="CI35" t="n">
+        <v>0.9941270805491241</v>
+      </c>
+      <c r="CJ35" t="n">
+        <v>0.9931361968486941</v>
+      </c>
+      <c r="CK35" t="n">
+        <v>0.004374522818913347</v>
+      </c>
+      <c r="CL35" t="n">
+        <v>0.9958340258641876</v>
+      </c>
+      <c r="CM35" t="n">
+        <v>0.9951219512195122</v>
+      </c>
+      <c r="CN35" t="n">
+        <v>0.003105156172485895</v>
+      </c>
+      <c r="CO35" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 0.9951219512195122, 0.9903381642512077, 0.9951690821256038, 1.0, 0.9951219512195122</t>
+        </is>
+      </c>
+      <c r="CP35" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9824561403508771, 0.9910714285714286, 1.0, 1.0, 0.9824561403508771</t>
+        </is>
+      </c>
+      <c r="CQ35" t="n">
+        <v>0.9924477359644371</v>
+      </c>
+      <c r="CR35" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="CS35" t="n">
+        <v>0.007312916502704701</v>
+      </c>
+      <c r="CT35" t="n">
+        <v>0.995839014290764</v>
+      </c>
+      <c r="CU35" t="n">
+        <v>0.9951219512195122</v>
+      </c>
+      <c r="CV35" t="n">
+        <v>0.003090961541402253</v>
+      </c>
+      <c r="CW35" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 0.9902912621359223, 0.9951456310679612, 1.0, 1.0, 0.9902912621359223</t>
+        </is>
+      </c>
+      <c r="CX35" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9823008849557522, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY35" t="n">
+        <v>0.9924146649810366</v>
+      </c>
+      <c r="CZ35" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA35" t="n">
+        <v>0.005653774911503901</v>
+      </c>
+      <c r="DB35" t="n">
+        <v>0.995835729508474</v>
+      </c>
+      <c r="DC35" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="DD35" t="n">
+        <v>0.004044244559048504</v>
+      </c>
+      <c r="DE35" t="inlineStr">
+        <is>
+          <t>0.9998489099935247, 1.0, 0.9995918893375719, 0.9995918893375719, 0.9997637254059627, 1.0, 0.999849643440158</t>
+        </is>
+      </c>
+      <c r="DF35" t="n">
+        <v>0.9998065796449699</v>
+      </c>
+      <c r="DG35" t="n">
+        <v>0.9998489099935247</v>
+      </c>
+      <c r="DH35" t="n">
+        <v>0.000156975684344003</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Logit_no_fragmentation_smote_9-dim_vae</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 9, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.0790071604095478}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.008367466805612848, 'beta_warmup_steps': 1817, 'beta_start': 0.005364676165587271, 'beta_end': 0.06463895620675993}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9354545454545454</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.9777777777777777</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.835016835016835</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.8734177215189873</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.7379679144385026</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.9163279526187434</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.8087873970226911</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.8472593194750899</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.9470899470899471</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.8211009174311926</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.8796068796068797</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>3.8589022159576416, 3.530196189880371, 3.4565651416778564, 2.9641802310943604, 3.4311227798461914, 3.0074338912963867, 3.170520067214966</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.345560073852539</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.431122779846191</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.2946360116818932</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>0.016987085342407227, 0.016974687576293945, 0.017000198364257812, 0.017000675201416016, 0.01699995994567871, 0.01700592041015625, 0.017000436782836914</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.01699556623186384</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.01700019836425781</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.004019038494257e-05</v>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>0.7777777777777778, 0.7924528301886793, 0.8867924528301887, 0.7358490566037735, 0.8867924528301887, 0.8490566037735849, 0.7924528301886793</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>0.7846153846153847, 0.8131868131868132, 0.8772893772893773, 0.7747252747252746, 0.9001831501831502, 0.8287545787545787, 0.858974358974359</t>
+        </is>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.8339612768184198</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.8287545787545787</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.04357411444309101</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.8173105720275533</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0.05358292508726654</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.6857142857142857, 0.7999999999999999, 0.631578947368421, 0.8125000000000001, 0.7333333333333334, 0.717948717948718</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>0.8333333333333333, 0.8450704225352113, 0.9210526315789475, 0.7941176470588235, 0.9189189189189189, 0.8947368421052632, 0.835820895522388</t>
+        </is>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.8632929558646979</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.8450704225352113</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.04502177732932641</v>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>0.75, 0.7653923541247485, 0.8605263157894737, 0.7128482972136223, 0.8657094594594594, 0.8140350877192983, 0.7768848067355529</t>
+        </is>
+      </c>
+      <c r="AU36" t="n">
+        <v>0.7921994744345936</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0.7768848067355529</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0.05288752873566237</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0.7211059930044892</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.717948717948718</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.06206898257946832</v>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>0.5714285714285714, 0.5714285714285714, 0.75, 0.5, 0.7222222222222222, 0.6875, 0.56</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.9375, 0.9459459459459459, 0.9310344827586207, 0.9714285714285714, 0.918918918918919, 1.0</t>
+        </is>
+      </c>
+      <c r="BC36" t="n">
+        <v>0.9448455468775666</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0.02914291995178513</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0.6232256235827665</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0.08827810562607911</v>
+      </c>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>0.8, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ36" t="inlineStr">
+        <is>
+          <t>0.7692307692307693, 0.7692307692307693, 0.8974358974358975, 0.6923076923076923, 0.8717948717948718, 0.8717948717948718, 0.717948717948718</t>
+        </is>
+      </c>
+      <c r="BK36" t="n">
+        <v>0.7985347985347986</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0.07560354373827947</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0.8693877551020408</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0.06848147647168375</v>
+      </c>
+      <c r="BQ36" t="inlineStr">
+        <is>
+          <t>0.905982905982906, 0.8772893772893773, 0.9597069597069597, 0.8772893772893773, 0.9194139194139194, 0.9230769230769231, 0.9688644688644689</t>
+        </is>
+      </c>
+      <c r="BR36" t="n">
+        <v>0.9188034188034189</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0.9194139194139194</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>0.03340025828829504</v>
+      </c>
+      <c r="BU36" t="inlineStr">
+        <is>
+          <t>0.7987421383647799, 0.8589341692789969, 0.8338557993730408, 0.8119122257053292, 0.8056426332288401, 0.8589341692789969, 0.8181818181818182</t>
+        </is>
+      </c>
+      <c r="BV36" t="inlineStr">
+        <is>
+          <t>0.8289072039072038, 0.8813725490196078, 0.8567873303167421, 0.8418300653594771, 0.8188285570638512, 0.8663901458019105, 0.8535947712418301</t>
+        </is>
+      </c>
+      <c r="BW36" t="n">
+        <v>0.8496729461015177</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>0.8535947712418301</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0.01998008983428226</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0.8266004219159716</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CB36" t="n">
+        <v>0.02282076687375691</v>
+      </c>
+      <c r="CC36" t="inlineStr">
+        <is>
+          <t>0.7009345794392522, 0.7783251231527094, 0.7439613526570049, 0.7196261682242989, 0.6990291262135924, 0.7692307692307693, 0.7314814814814815</t>
+        </is>
+      </c>
+      <c r="CD36" t="inlineStr">
+        <is>
+          <t>0.8483412322274881, 0.896551724137931, 0.8770301624129929, 0.8584905660377358, 0.8564814814814815, 0.8984198645598194, 0.8625592417061613</t>
+        </is>
+      </c>
+      <c r="CE36" t="n">
+        <v>0.8711248960805158</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>0.8625592417061613</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>0.01848911927123929</v>
+      </c>
+      <c r="CH36" t="inlineStr">
+        <is>
+          <t>0.7746379058333701, 0.8374384236453203, 0.8104957575349989, 0.7890583671310174, 0.7777553038475369, 0.8338253168952943, 0.7970203615938214</t>
+        </is>
+      </c>
+      <c r="CI36" t="n">
+        <v>0.8028902052116227</v>
+      </c>
+      <c r="CJ36" t="n">
+        <v>0.7970203615938214</v>
+      </c>
+      <c r="CK36" t="n">
+        <v>0.0234950920513005</v>
+      </c>
+      <c r="CL36" t="n">
+        <v>0.7346555143427299</v>
+      </c>
+      <c r="CM36" t="n">
+        <v>0.7314814814814815</v>
+      </c>
+      <c r="CN36" t="n">
+        <v>0.02886267565600294</v>
+      </c>
+      <c r="CO36" t="inlineStr">
+        <is>
+          <t>0.5769230769230769, 0.6694915254237288, 0.6311475409836066, 0.5968992248062015, 0.5950413223140496, 0.6818181818181818, 0.6030534351145038</t>
+        </is>
+      </c>
+      <c r="CP36" t="inlineStr">
+        <is>
+          <t>0.9521276595744681, 0.9701492537313433, 0.9593908629441624, 0.9578947368421052, 0.9343434343434344, 0.9521531100478469, 0.9680851063829787</t>
+        </is>
+      </c>
+      <c r="CQ36" t="n">
+        <v>0.9563063091237627</v>
+      </c>
+      <c r="CR36" t="n">
+        <v>0.9578947368421052</v>
+      </c>
+      <c r="CS36" t="n">
+        <v>0.01108076066500589</v>
+      </c>
+      <c r="CT36" t="n">
+        <v>0.6220534724833354</v>
+      </c>
+      <c r="CU36" t="n">
+        <v>0.6030534351145038</v>
+      </c>
+      <c r="CV36" t="n">
+        <v>0.03715803679066502</v>
+      </c>
+      <c r="CW36" t="inlineStr">
+        <is>
+          <t>0.8928571428571429, 0.9294117647058824, 0.9058823529411765, 0.9058823529411765, 0.8470588235294118, 0.8823529411764706, 0.9294117647058824</t>
+        </is>
+      </c>
+      <c r="CX36" t="inlineStr">
+        <is>
+          <t>0.7649572649572649, 0.8333333333333334, 0.8076923076923077, 0.7777777777777778, 0.7905982905982906, 0.8504273504273504, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="CY36" t="n">
+        <v>0.8003663003663003</v>
+      </c>
+      <c r="CZ36" t="n">
+        <v>0.7905982905982906</v>
+      </c>
+      <c r="DA36" t="n">
+        <v>0.02931674530779725</v>
+      </c>
+      <c r="DB36" t="n">
+        <v>0.8989795918367347</v>
+      </c>
+      <c r="DC36" t="n">
+        <v>0.9058823529411765</v>
+      </c>
+      <c r="DD36" t="n">
+        <v>0.02661156190217822</v>
+      </c>
+      <c r="DE36" t="inlineStr">
+        <is>
+          <t>0.9226190476190477, 0.9563599798893917, 0.912569130216189, 0.9332327802916038, 0.9040723981900451, 0.9536953242835596, 0.9249874308697837</t>
+        </is>
+      </c>
+      <c r="DF36" t="n">
+        <v>0.9296480130513743</v>
+      </c>
+      <c r="DG36" t="n">
+        <v>0.9249874308697837</v>
+      </c>
+      <c r="DH36" t="n">
+        <v>0.01821138027942489</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smote_9-dim_vae</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 9, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.0790071604095478}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.008367466805612848, 'beta_warmup_steps': 1817, 'beta_start': 0.005364676165587271, 'beta_end': 0.06463895620675993}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9563636363636363</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.8636363636363638</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.9898989898989899</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.9811320754716981</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.9997096736732087</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.9871177618737801</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.9890837301126467</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.9953917050691244</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.9908256880733946</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.9931034482758622</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>5.622931718826294, 5.402719259262085, 5.45527982711792, 4.953309059143066, 5.399834156036377, 4.918544769287109, 5.1355602741241455</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>5.269739866256714</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>5.399834156036377</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.2493558042425689</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>0.017999887466430664, 0.018000125885009766, 0.017002344131469727, 0.017998695373535156, 0.025998353958129883, 0.017000913619995117, 0.01900005340576172</t>
+        </is>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.01900005340576172</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.01799988746643066</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.00292688322063306</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.8301886792452831, 0.9056603773584906, 0.9056603773584906, 0.9622641509433962, 0.9433962264150944, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>0.7897435897435897, 0.8159340659340659, 0.8672161172161172, 0.9130036630036631, 0.9285714285714286, 0.9157509157509157, 0.9130036630036631</t>
+        </is>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.8776033490319206</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.9130036630036631</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.05097573484641452</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.8953778576420086</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.05047879817451398</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>0.6875, 0.7096774193548386, 0.8148148148148148, 0.8387096774193549, 0.923076923076923, 0.888888888888889, 0.8387096774193549</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>0.868421052631579, 0.8799999999999999, 0.9367088607594937, 0.9333333333333333, 0.975, 0.9620253164556962, 0.9333333333333333</t>
+        </is>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.9269745566447763</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.03653910925400558</v>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>0.7779605263157895, 0.7948387096774192, 0.8757618377871542, 0.886021505376344, 0.9490384615384615, 0.9254571026722926, 0.886021505376344</t>
+        </is>
+      </c>
+      <c r="AU37" t="n">
+        <v>0.8707285212491149</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0.8860215053763441</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0.05853681840084539</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0.8144824858534536</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0.08072151629498937</v>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>0.6470588235294118, 0.6470588235294118, 0.8461538461538461, 0.7647058823529411, 1.0, 0.9230769230769231, 0.7647058823529411</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.9166666666666666, 0.925, 0.9722222222222222, 0.9512195121951219, 0.95, 0.9722222222222222</t>
+        </is>
+      </c>
+      <c r="BC37" t="n">
+        <v>0.9398889307425894</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0.02773901022876138</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0.7989657401422107</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0.1233716655685377</v>
+      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.7857142857142857, 0.9285714285714286, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.8461538461538461, 0.9487179487179487, 0.8974358974358975, 1.0, 0.9743589743589743, 0.8974358974358975</t>
+        </is>
+      </c>
+      <c r="BK37" t="n">
+        <v>0.9157509157509158</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>0.05603318146805258</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>0.8394557823129251</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0.06922750603106696</v>
+      </c>
+      <c r="BQ37" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.9065934065934066, 0.9798534798534798, 0.9597069597069597, 0.9853479853479854, 0.9652014652014653, 0.9615384615384616</t>
+        </is>
+      </c>
+      <c r="BR37" t="n">
+        <v>0.958137100994244</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>0.02396856617603096</v>
+      </c>
+      <c r="BU37" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 0.9937304075235109, 0.987460815047022, 0.9905956112852664, 0.9843260188087775, 0.9968652037617555, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV37" t="inlineStr">
+        <is>
+          <t>0.9919108669108669, 0.9919808949220714, 0.9839617898441428, 0.9898441427853193, 0.9818250377073907, 0.9978632478632479, 0.9941176470588236</t>
+        </is>
+      </c>
+      <c r="BW37" t="n">
+        <v>0.9902148038702662</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>0.9919108669108669</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>0.005200993562054467</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0.9919362788588553</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0.9937106918238994</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>0.004386656135151361</v>
+      </c>
+      <c r="CC37" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 0.9882352941176471, 0.9764705882352941, 0.9824561403508771, 0.9707602339181286, 0.9941520467836257, 0.9940828402366864</t>
+        </is>
+      </c>
+      <c r="CD37" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 0.9957264957264957, 0.9914529914529915, 0.9935760171306209, 0.9892933618843683, 0.9978586723768736, 0.9978678038379531</t>
+        </is>
+      </c>
+      <c r="CE37" t="n">
+        <v>0.9945002625908284</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0.00299710459737514</v>
+      </c>
+      <c r="CH37" t="inlineStr">
+        <is>
+          <t>0.9919108669108669, 0.9919808949220714, 0.9839617898441428, 0.988016078740749, 0.9800267979012485, 0.9960053595802496, 0.9959753220373198</t>
+        </is>
+      </c>
+      <c r="CI37" t="n">
+        <v>0.9896967299909497</v>
+      </c>
+      <c r="CJ37" t="n">
+        <v>0.9919108669108669</v>
+      </c>
+      <c r="CK37" t="n">
+        <v>0.005587755118421634</v>
+      </c>
+      <c r="CL37" t="n">
+        <v>0.984893197391071</v>
+      </c>
+      <c r="CM37" t="n">
+        <v>0.9880952380952381</v>
+      </c>
+      <c r="CN37" t="n">
+        <v>0.008178532451665093</v>
+      </c>
+      <c r="CO37" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 0.9882352941176471, 0.9764705882352941, 0.9767441860465116, 0.9651162790697675, 0.9883720930232558, 1.0</t>
+        </is>
+      </c>
+      <c r="CP37" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 0.9957264957264957, 0.9914529914529915, 0.9957081545064378, 0.9914163090128756, 1.0, 0.9957446808510638</t>
+        </is>
+      </c>
+      <c r="CQ37" t="n">
+        <v>0.9951107324680514</v>
+      </c>
+      <c r="CR37" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>0.002737305855439023</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>0.9832905255125306</v>
+      </c>
+      <c r="CU37" t="n">
+        <v>0.9880952380952381</v>
+      </c>
+      <c r="CV37" t="n">
+        <v>0.01050329338966803</v>
+      </c>
+      <c r="CW37" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 0.9882352941176471, 0.9764705882352941, 0.9882352941176471, 0.9764705882352941, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CX37" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 0.9957264957264957, 0.9914529914529915, 0.9914529914529915, 0.9871794871794872, 0.9957264957264957, 1.0</t>
+        </is>
+      </c>
+      <c r="CY37" t="n">
+        <v>0.9938949938949939</v>
+      </c>
+      <c r="CZ37" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="DA37" t="n">
+        <v>0.003861144884210462</v>
+      </c>
+      <c r="DB37" t="n">
+        <v>0.9865346138455383</v>
+      </c>
+      <c r="DC37" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="DD37" t="n">
+        <v>0.007511879501055483</v>
+      </c>
+      <c r="DE37" t="inlineStr">
+        <is>
+          <t>0.9996438746438746, 0.9992961287078934, 0.9980392156862745, 0.9994469582704878, 0.998139768728004, 1.0, 0.9997486173956762</t>
+        </is>
+      </c>
+      <c r="DF37" t="n">
+        <v>0.99918779477603</v>
+      </c>
+      <c r="DG37" t="n">
+        <v>0.9994469582704878</v>
+      </c>
+      <c r="DH37" t="n">
+        <v>0.0007249337568575485</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Logit_splashing_smote_10-dim_vae</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 10, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.08982791849888751}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.009978392812880254, 'beta_warmup_steps': 1506, 'beta_start': 0.01072668832819871, 'beta_end': 0.05004010460787294}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.803921568627451</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.8282828282828283</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8858024691358024</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.7474747474747475</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.7418981481481481</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.6296296296296297</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.8316498316498316</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.9080459770114943</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.8229166666666666</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.8633879781420765</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.9219990079365078</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.8220448662640207</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.8352678571428571</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.7235772357723578</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.8476190476190476</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.7807017543859649</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>4.029250383377075, 3.3552403450012207, 4.17245888710022, 3.6421539783477783, 3.756192684173584, 3.2844629287719727, 3.069432497024536</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.615598814828055</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.642153978347778</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.3736705438922107</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>0.019001245498657227, 0.018000125885009766, 0.01900172233581543, 0.01799798011779785, 0.01800060272216797, 0.017999887466430664, 0.01800084114074707</t>
+        </is>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.01828605788094657</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.01800060272216797</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.0004524759799651739</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7924528301886793, 0.8301886792452831, 0.7547169811320755, 0.8113207547169812, 0.7924528301886793, 0.8301886792452831</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>0.9451127819548872, 0.8023809523809524, 0.8444272445820433, 0.7739938080495357, 0.818111455108359, 0.8150154798761611, 0.8560371517027863</t>
+        </is>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.836439839093532</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.818111455108359</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.05086692610938172</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.8222521713087751</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.05543777357646075</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>0.9565217391304348, 0.8307692307692307, 0.8571428571428571, 0.7868852459016393, 0.84375, 0.819672131147541, 0.8524590163934426</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>0.9230769230769231, 0.7317073170731708, 0.7906976744186046, 0.7111111111111111, 0.761904761904762, 0.7555555555555555, 0.7999999999999999</t>
+        </is>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.7820076204485895</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.761904761904762</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.06432069553484643</v>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>0.939799331103679, 0.7812382739212007, 0.8239202657807309, 0.7489981785063753, 0.8028273809523809, 0.7876138433515483, 0.8262295081967213</t>
+        </is>
+      </c>
+      <c r="AU38" t="n">
+        <v>0.8158038259732336</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0.8028273809523809</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0.05627774478328287</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0.8496000314978779</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0.04886565409770468</v>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>0.9705882352941176, 0.9, 0.9310344827586207, 0.8888888888888888, 0.9, 0.9259259259259259, 0.9629629629629629</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>0.9, 0.6521739130434783, 0.7083333333333334, 0.6153846153846154, 0.6956521739130435, 0.6538461538461539, 0.6923076923076923</t>
+        </is>
+      </c>
+      <c r="BC38" t="n">
+        <v>0.7025282688326168</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0.08592359567222273</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0.9256286422615022</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0.02953930089890393</v>
+      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.7714285714285715, 0.7941176470588235, 0.7058823529411765, 0.7941176470588235, 0.7352941176470589, 0.7647058823529411</t>
+        </is>
+      </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>0.9473684210526315, 0.8333333333333334, 0.8947368421052632, 0.8421052631578947, 0.8421052631578947, 0.8947368421052632, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="BK38" t="n">
+        <v>0.8859649122807017</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>0.04521708910443285</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>0.7869147659063626</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0.07008748403512448</v>
+      </c>
+      <c r="BQ38" t="inlineStr">
+        <is>
+          <t>0.9654135338345865, 0.8825396825396825, 0.9256965944272446, 0.868421052631579, 0.9272445820433437, 0.8823529411764706, 0.8761609907120743</t>
+        </is>
+      </c>
+      <c r="BR38" t="n">
+        <v>0.9039756253378545</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>0.8825396825396825</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>0.03327951557528172</v>
+      </c>
+      <c r="BU38" t="inlineStr">
+        <is>
+          <t>0.8018867924528302, 0.8369905956112853, 0.7931034482758621, 0.8181818181818182, 0.8275862068965517, 0.8338557993730408, 0.8401253918495298</t>
+        </is>
+      </c>
+      <c r="BV38" t="inlineStr">
+        <is>
+          <t>0.8185409022231815, 0.8537013264869491, 0.8138370994071655, 0.8372497637254059, 0.8505241000085918, 0.8433929031703755, 0.8542400549875419</t>
+        </is>
+      </c>
+      <c r="BW38" t="n">
+        <v>0.8387837357156016</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>0.8433929031703755</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>0.0153761082722038</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>0.8216757218058455</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CB38" t="n">
+        <v>0.01681159340664537</v>
+      </c>
+      <c r="CC38" t="inlineStr">
+        <is>
+          <t>0.8319999999999999, 0.8624338624338623, 0.8225806451612903, 0.8457446808510638, 0.8525469168900803, 0.8630490956072351, 0.8668407310704961</t>
+        </is>
+      </c>
+      <c r="CD38" t="inlineStr">
+        <is>
+          <t>0.7586206896551724, 0.8, 0.7518796992481204, 0.7786259541984732, 0.7924528301886792, 0.7888446215139443, 0.8</t>
+        </is>
+      </c>
+      <c r="CE38" t="n">
+        <v>0.7814891135434842</v>
+      </c>
+      <c r="CF38" t="n">
+        <v>0.7888446215139443</v>
+      </c>
+      <c r="CG38" t="n">
+        <v>0.01799798529390205</v>
+      </c>
+      <c r="CH38" t="inlineStr">
+        <is>
+          <t>0.7953103448275861, 0.8312169312169312, 0.7872301722047053, 0.8121853175247685, 0.8224998735393798, 0.8259468585605897, 0.8334203655352481</t>
+        </is>
+      </c>
+      <c r="CI38" t="n">
+        <v>0.8154014090584584</v>
+      </c>
+      <c r="CJ38" t="n">
+        <v>0.8224998735393798</v>
+      </c>
+      <c r="CK38" t="n">
+        <v>0.01666485150334104</v>
+      </c>
+      <c r="CL38" t="n">
+        <v>0.8493137045734326</v>
+      </c>
+      <c r="CM38" t="n">
+        <v>0.8525469168900803</v>
+      </c>
+      <c r="CN38" t="n">
+        <v>0.01560956021512556</v>
+      </c>
+      <c r="CO38" t="inlineStr">
+        <is>
+          <t>0.9176470588235294, 0.9421965317919075, 0.9216867469879518, 0.9352941176470588, 0.9520958083832335, 0.9226519337016574, 0.9378531073446328</t>
+        </is>
+      </c>
+      <c r="CP38" t="inlineStr">
+        <is>
+          <t>0.668918918918919, 0.7123287671232876, 0.6535947712418301, 0.6845637583892618, 0.6907894736842105, 0.717391304347826, 0.7183098591549296</t>
+        </is>
+      </c>
+      <c r="CQ38" t="n">
+        <v>0.6922709789800379</v>
+      </c>
+      <c r="CR38" t="n">
+        <v>0.6907894736842105</v>
+      </c>
+      <c r="CS38" t="n">
+        <v>0.02334258142729402</v>
+      </c>
+      <c r="CT38" t="n">
+        <v>0.9327750435257103</v>
+      </c>
+      <c r="CU38" t="n">
+        <v>0.9352941176470588</v>
+      </c>
+      <c r="CV38" t="n">
+        <v>0.01164027771009054</v>
+      </c>
+      <c r="CW38" t="inlineStr">
+        <is>
+          <t>0.7609756097560976, 0.7951219512195122, 0.7427184466019418, 0.7718446601941747, 0.7718446601941747, 0.8106796116504854, 0.8058252427184466</t>
+        </is>
+      </c>
+      <c r="CX38" t="inlineStr">
+        <is>
+          <t>0.8761061946902655, 0.9122807017543859, 0.8849557522123894, 0.9026548672566371, 0.9292035398230089, 0.8761061946902655, 0.9026548672566371</t>
+        </is>
+      </c>
+      <c r="CY38" t="n">
+        <v>0.8977088739547986</v>
+      </c>
+      <c r="CZ38" t="n">
+        <v>0.9026548672566371</v>
+      </c>
+      <c r="DA38" t="n">
+        <v>0.01831927735647414</v>
+      </c>
+      <c r="DB38" t="n">
+        <v>0.7798585974764046</v>
+      </c>
+      <c r="DC38" t="n">
+        <v>0.7718446601941747</v>
+      </c>
+      <c r="DD38" t="n">
+        <v>0.02305761715195326</v>
+      </c>
+      <c r="DE38" t="inlineStr">
+        <is>
+          <t>0.9038851715950789, 0.9260162601626016, 0.9083898960391785, 0.9206332159120201, 0.9218360683907553, 0.9277429332416873, 0.9178408798006703</t>
+        </is>
+      </c>
+      <c r="DF38" t="n">
+        <v>0.9180492035917132</v>
+      </c>
+      <c r="DG38" t="n">
+        <v>0.9206332159120201</v>
+      </c>
+      <c r="DH38" t="n">
+        <v>0.008215188661482853</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_smote_10-dim_vae</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 10, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.08982791849888751}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.009978392812880254, 'beta_warmup_steps': 1506, 'beta_start': 0.01072668832819871, 'beta_end': 0.05004010460787294}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.863608809860578</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.849537037037037</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.9998759920634921</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>5.873850584030151, 5.113691329956055, 5.957071542739868, 5.434452295303345, 5.57613730430603, 5.0813117027282715, 4.8362390995025635</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>5.410393408366612</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>5.434452295303345</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.3905453088885183</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>0.018999576568603516, 0.018999814987182617, 0.017998695373535156, 0.019149065017700195, 0.019000768661499023, 0.021157264709472656, 0.01800060272216797</t>
+        </is>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.0190436840057373</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.01899981498718262</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.0009757092686143515</v>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8113207547169812, 0.9245283018867925, 0.9245283018867925, 0.9056603773584906, 0.9056603773584906, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8301587301587301, 0.9295665634674922, 0.9411764705882353, 0.891640866873065, 0.914860681114551, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.9045295311106897</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.914860681114551</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.03848997460521691</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.9030647898572427</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.04343202722774474</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8437500000000001, 0.9393939393939394, 0.9375, 0.9275362318840579, 0.923076923076923, 0.9117647058823528</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.761904761904762, 0.9, 0.9047619047619047, 0.8648648648648649, 0.8780487804878049, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.8708757170888107</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.05371731097797821</v>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.802827380952381, 0.9196969696969697, 0.9211309523809523, 0.8962005483744614, 0.900562851782364, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AU39" t="n">
+        <v>0.8965267172915122</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0.9005628517823639</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0.04494772385557622</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0.9221777174942137</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0.9275362318840579</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0.03649752050381829</v>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9310344827586207, 0.96875, 1.0, 0.9142857142857143, 0.967741935483871, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>1.0, 0.6666666666666666, 0.8571428571428571, 0.8260869565217391, 0.8888888888888888, 0.8181818181818182, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BC39" t="n">
+        <v>0.8427246357942664</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0.09176874502202215</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0.9485032549080722</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0.9459459459459459</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0.02991471489912909</v>
+      </c>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>1.0, 0.7714285714285715, 0.9117647058823529, 0.8823529411764706, 0.9411764705882353, 0.8823529411764706, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ39" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8888888888888888, 0.9473684210526315, 1.0, 0.8421052631578947, 0.9473684210526315, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK39" t="n">
+        <v>0.9089390142021722</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0.05448846736548148</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>0.9001200480192078</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>0.06450433769860765</v>
+      </c>
+      <c r="BQ39" t="inlineStr">
+        <is>
+          <t>1.0, 0.9206349206349207, 0.9643962848297214, 0.9798761609907122, 0.9411764705882353, 0.9303405572755419, 0.9210526315789473</t>
+        </is>
+      </c>
+      <c r="BR39" t="n">
+        <v>0.9510681465568683</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>0.02867666507087715</v>
+      </c>
+      <c r="BU39" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV39" t="inlineStr">
+        <is>
+          <t>0.9931361968486941, 0.9956140350877193, 0.995575221238938, 0.995575221238938, 0.9931480367729186, 0.9975728155339806, 0.9931480367729186</t>
+        </is>
+      </c>
+      <c r="BW39" t="n">
+        <v>0.9948242233563011</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>0.001593522315265486</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>0.9955189031311348</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB39" t="n">
+        <v>0.001554585969714499</v>
+      </c>
+      <c r="CC39" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 0.9975669099756691, 0.9975786924939467, 0.9975786924939467, 0.9951456310679612, 0.9975669099756691, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CD39" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9955947136563876, 0.9955555555555555, 0.9955555555555555, 0.9911504424778761, 0.9955947136563876, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CE39" t="n">
+        <v>0.993678837979645</v>
+      </c>
+      <c r="CF39" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG39" t="n">
+        <v>0.002189704754299955</v>
+      </c>
+      <c r="CH39" t="inlineStr">
+        <is>
+          <t>0.9931361968486941, 0.9965808118160284, 0.9965671240247511, 0.9965671240247511, 0.9931480367729186, 0.9965808118160284, 0.9931480367729186</t>
+        </is>
+      </c>
+      <c r="CI39" t="n">
+        <v>0.9951040202965844</v>
+      </c>
+      <c r="CJ39" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK39" t="n">
+        <v>0.001697361129784571</v>
+      </c>
+      <c r="CL39" t="n">
+        <v>0.9965292026135237</v>
+      </c>
+      <c r="CM39" t="n">
+        <v>0.9975669099756691</v>
+      </c>
+      <c r="CN39" t="n">
+        <v>0.001205074276694183</v>
+      </c>
+      <c r="CO39" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 0.9951456310679612, 0.9951690821256038, 0.9951690821256038, 0.9951456310679612, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CP39" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 1.0, 1.0, 0.9911504424778761, 0.9912280701754386, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CQ39" t="n">
+        <v>0.994954199658438</v>
+      </c>
+      <c r="CR39" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="CS39" t="n">
+        <v>0.004369865154029812</v>
+      </c>
+      <c r="CT39" t="n">
+        <v>0.9958424298106577</v>
+      </c>
+      <c r="CU39" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>0.001697387023507938</v>
+      </c>
+      <c r="CW39" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 1.0, 1.0, 0.9951456310679612, 0.9951456310679612, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CX39" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9912280701754386, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY39" t="n">
+        <v>0.9924257546521169</v>
+      </c>
+      <c r="CZ39" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA39" t="n">
+        <v>0.003092288713291248</v>
+      </c>
+      <c r="DB39" t="n">
+        <v>0.9972226920604852</v>
+      </c>
+      <c r="DC39" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="DD39" t="n">
+        <v>0.002405231718970799</v>
+      </c>
+      <c r="DE39" t="inlineStr">
+        <is>
+          <t>0.9997194042736888, 1.0, 0.9997637254059627, 0.9997637254059627, 0.9996778073717674, 1.0, 0.9998066844230604</t>
+        </is>
+      </c>
+      <c r="DF39" t="n">
+        <v>0.9998187638400632</v>
+      </c>
+      <c r="DG39" t="n">
+        <v>0.9997637254059627</v>
+      </c>
+      <c r="DH39" t="n">
+        <v>0.000120498080300903</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Logit_no_fragmentation_smote_10-dim_vae</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 10, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.08982791849888751}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.009978392812880254, 'beta_warmup_steps': 1506, 'beta_start': 0.01072668832819871, 'beta_end': 0.05004010460787294}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.7058823529411764</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9218181818181819</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.7771836007130124</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.8318181818181818</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.7636363636363637</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.8383838383838383</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.6260162601626016</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.9746835443037974</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.7623762376237624</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.9530252003251655</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.8199636290159629</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.8818371849959354</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.9885057471264368</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.7889908256880734</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.8775510204081634</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>3.8373231887817383, 4.249330282211304, 3.540604591369629, 3.2759695053100586, 4.218264579772949, 3.924138307571411, 4.491013526916504</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.933806283133371</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.924138307571411</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.3941919552262355</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>0.017000436782836914, 0.017000436782836914, 0.016000032424926758, 0.017000436782836914, 0.017000198364257812, 0.015999317169189453, 0.01599860191345215</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.01657135146004813</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.01700019836425781</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.0004953963813935263</v>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7358490566037735, 0.8490566037735849, 0.8301886792452831, 0.8301886792452831, 0.8490566037735849, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>0.9025641025641026, 0.728937728937729, 0.8974358974358974, 0.8159340659340659, 0.8159340659340659, 0.8287545787545787, 0.9358974358974359</t>
+        </is>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.8464939822082679</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.8287545787545787</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.06517437131989</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.8412698412698412</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.05055987725706539</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>0.8235294117647058, 0.588235294117647, 0.7777777777777778, 0.7096774193548386, 0.7096774193548386, 0.7333333333333334, 0.8484848484848484</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>0.9189189189189189, 0.8055555555555556, 0.8857142857142858, 0.8799999999999999, 0.8799999999999999, 0.8947368421052632, 0.9315068493150686</t>
+        </is>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.885204635944156</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.8857142857142858</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.03735892131760704</v>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>0.8712241653418124, 0.6968954248366013, 0.8317460317460318, 0.7948387096774192, 0.7948387096774192, 0.8140350877192983, 0.8899958488999584</t>
+        </is>
+      </c>
+      <c r="AU40" t="n">
+        <v>0.8133677111283629</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0.8140350877192983</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0.05832163298260504</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0.7415307863125699</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0.08024317551506295</v>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>0.7368421052631579, 0.5, 0.6363636363636364, 0.6470588235294118, 0.6470588235294118, 0.6875, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8787878787878788, 1.0, 0.9166666666666666, 0.9166666666666666, 0.918918918918919, 1.0</t>
+        </is>
+      </c>
+      <c r="BC40" t="n">
+        <v>0.9432098146383862</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0.918918918918919</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0.04374579062798852</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0.6559522134212535</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0.07458897087378759</v>
+      </c>
+      <c r="BI40" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.7142857142857143, 1.0, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ40" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.7435897435897436, 0.7948717948717948, 0.8461538461538461, 0.8461538461538461, 0.8717948717948718, 0.8717948717948718</t>
+        </is>
+      </c>
+      <c r="BK40" t="n">
+        <v>0.8351648351648352</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>0.04516054214629287</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>0.8578231292517007</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>0.1084516755558075</v>
+      </c>
+      <c r="BQ40" t="inlineStr">
+        <is>
+          <t>0.9606837606837608, 0.8827838827838828, 0.9688644688644689, 0.9157509157509157, 0.8974358974358975, 0.912087912087912, 0.9871794871794872</t>
+        </is>
+      </c>
+      <c r="BR40" t="n">
+        <v>0.9321123321123321</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>0.9157509157509157</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>0.03684690727734066</v>
+      </c>
+      <c r="BU40" t="inlineStr">
+        <is>
+          <t>0.839622641509434, 0.8652037617554859, 0.8307210031347962, 0.8620689655172413, 0.8307210031347962, 0.8401253918495298, 0.8432601880877743</t>
+        </is>
+      </c>
+      <c r="BV40" t="inlineStr">
+        <is>
+          <t>0.871947496947497, 0.8893916540975364, 0.8696329813976873, 0.861035696329814, 0.8471593765711413, 0.8535696329813977, 0.8631975867269985</t>
+        </is>
+      </c>
+      <c r="BW40" t="n">
+        <v>0.8651334892931531</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>0.8631975867269985</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>0.01271930937055598</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>0.8445318507127225</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0.8401253918495298</v>
+      </c>
+      <c r="CB40" t="n">
+        <v>0.01288128023814054</v>
+      </c>
+      <c r="CC40" t="inlineStr">
+        <is>
+          <t>0.7559808612440192, 0.7881773399014779, 0.75, 0.7684210526315789, 0.7352941176470589, 0.7462686567164178, 0.7549019607843137</t>
+        </is>
+      </c>
+      <c r="CD40" t="inlineStr">
+        <is>
+          <t>0.8805620608899297, 0.9011494252873563, 0.8720379146919431, 0.9017857142857143, 0.8755760368663594, 0.8832951945080091, 0.8847926267281105</t>
+        </is>
+      </c>
+      <c r="CE40" t="n">
+        <v>0.885599853322489</v>
+      </c>
+      <c r="CF40" t="n">
+        <v>0.8832951945080091</v>
+      </c>
+      <c r="CG40" t="n">
+        <v>0.01082006587513415</v>
+      </c>
+      <c r="CH40" t="inlineStr">
+        <is>
+          <t>0.8182714610669745, 0.8446633825944171, 0.8110189573459716, 0.8351033834586465, 0.8054350772567092, 0.8147819256122135, 0.8198472937562121</t>
+        </is>
+      </c>
+      <c r="CI40" t="n">
+        <v>0.8213030687273063</v>
+      </c>
+      <c r="CJ40" t="n">
+        <v>0.8182714610669745</v>
+      </c>
+      <c r="CK40" t="n">
+        <v>0.01280370640628712</v>
+      </c>
+      <c r="CL40" t="n">
+        <v>0.7570062841321238</v>
+      </c>
+      <c r="CM40" t="n">
+        <v>0.7549019607843137</v>
+      </c>
+      <c r="CN40" t="n">
+        <v>0.01578070322467858</v>
+      </c>
+      <c r="CO40" t="inlineStr">
+        <is>
+          <t>0.632, 0.6779661016949152, 0.6183206106870229, 0.6952380952380952, 0.6302521008403361, 0.646551724137931, 0.6470588235294118</t>
+        </is>
+      </c>
+      <c r="CP40" t="inlineStr">
+        <is>
+          <t>0.9740932642487047, 0.9751243781094527, 0.9787234042553191, 0.9439252336448598, 0.95, 0.9507389162561576, 0.96</t>
+        </is>
+      </c>
+      <c r="CQ40" t="n">
+        <v>0.9618007423592134</v>
+      </c>
+      <c r="CR40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CS40" t="n">
+        <v>0.01308979892600431</v>
+      </c>
+      <c r="CT40" t="n">
+        <v>0.6496267794468161</v>
+      </c>
+      <c r="CU40" t="n">
+        <v>0.646551724137931</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>0.02553909441181043</v>
+      </c>
+      <c r="CW40" t="inlineStr">
+        <is>
+          <t>0.9404761904761905, 0.9411764705882353, 0.9529411764705882, 0.8588235294117647, 0.8823529411764706, 0.8823529411764706, 0.9058823529411765</t>
+        </is>
+      </c>
+      <c r="CX40" t="inlineStr">
+        <is>
+          <t>0.8034188034188035, 0.8376068376068376, 0.7863247863247863, 0.8632478632478633, 0.811965811965812, 0.8247863247863247, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="CY40" t="n">
+        <v>0.821123321123321</v>
+      </c>
+      <c r="CZ40" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="DA40" t="n">
+        <v>0.02289173780128533</v>
+      </c>
+      <c r="DB40" t="n">
+        <v>0.9091436574629851</v>
+      </c>
+      <c r="DC40" t="n">
+        <v>0.9058823529411765</v>
+      </c>
+      <c r="DD40" t="n">
+        <v>0.03360333266959944</v>
+      </c>
+      <c r="DE40" t="inlineStr">
+        <is>
+          <t>0.9438339438339439, 0.9622926093514329, 0.9364002011060836, 0.948265460030166, 0.918350930115636, 0.936299648064354, 0.9483660130718954</t>
+        </is>
+      </c>
+      <c r="DF40" t="n">
+        <v>0.9419726865105017</v>
+      </c>
+      <c r="DG40" t="n">
+        <v>0.9438339438339439</v>
+      </c>
+      <c r="DH40" t="n">
+        <v>0.01263815368606495</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smote_10-dim_vae</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 10, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.08982791849888751}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.009978392812880254, 'beta_warmup_steps': 1506, 'beta_start': 0.01072668832819871, 'beta_end': 0.05004010460787294}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9563636363636364</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.8636363636363638</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>5.613219976425171, 6.043100595474243, 5.340499639511108, 5.073040008544922, 6.070042133331299, 5.72535514831543, 6.287358999252319</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>5.736088071550641</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5.72535514831543</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.4001814493478241</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>0.019001245498657227, 0.016995906829833984, 0.017000436782836914, 0.016999244689941406, 0.018000125885009766, 0.01700115203857422, 0.018307924270629883</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.01761514799935477</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.01700115203857422</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.0007622401800146405</v>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.8490566037735849, 0.8867924528301887, 0.9433962264150944, 0.9245283018867925, 0.9433962264150944, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>0.8025641025641026, 0.8287545787545787, 0.8086080586080586, 0.9615384615384616, 0.8571428571428572, 0.9157509157509157, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.8714547357404502</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.05825684836973512</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.9007187780772687</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0.04171371304728344</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>0.7096774193548386, 0.7333333333333334, 0.75, 0.9032258064516129, 0.8333333333333333, 0.888888888888889, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>0.8831168831168831, 0.8947368421052632, 0.9268292682926831, 0.9600000000000001, 0.951219512195122, 0.9620253164556962, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.9321851776026113</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.02950955323912233</v>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>0.7963971512358609, 0.8140350877192983, 0.8384146341463415, 0.9316129032258065, 0.8922764227642277, 0.9254571026722926, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU41" t="n">
+        <v>0.872172977946211</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0.8922764227642277</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.05106328133110807</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.8121607782898106</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0.07385292194586215</v>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>0.6875, 0.6875, 0.9, 0.8235294117647058, 1.0, 0.9230769230769231, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.918918918918919, 0.8837209302325582, 1.0, 0.9069767441860465, 0.95, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC41" t="n">
+        <v>0.9324752012022514</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0.918918918918919</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0.0398961031549334</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0.8334437621202327</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0.1091139087891921</v>
+      </c>
+      <c r="BI41" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.6428571428571429, 1.0, 0.7142857142857143, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ41" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.8717948717948718, 0.9743589743589743, 0.9230769230769231, 1.0, 0.9743589743589743, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK41" t="n">
+        <v>0.9340659340659342</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>0.04719450083049496</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>0.8088435374149661</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>0.1170700667444841</v>
+      </c>
+      <c r="BQ41" t="inlineStr">
+        <is>
+          <t>0.9521367521367521, 0.9377289377289377, 0.976190476190476, 0.9743589743589745, 0.9835164835164835, 0.9285714285714285, 0.9542124542124542</t>
+        </is>
+      </c>
+      <c r="BR41" t="n">
+        <v>0.9581022152450724</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>0.9542124542124542</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>0.01918037397962903</v>
+      </c>
+      <c r="BU41" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 0.9937304075235109, 0.9905956112852664, 0.9937304075235109, 0.9968652037617555, 0.9937304075235109, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV41" t="inlineStr">
+        <is>
+          <t>0.9978632478632479, 0.9919808949220714, 0.986098541980895, 0.9919808949220714, 0.9941176470588236, 0.9957264957264957, 0.9919808949220714</t>
+        </is>
+      </c>
+      <c r="BW41" t="n">
+        <v>0.9928212310565252</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>0.9919808949220714</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>0.003440436716404149</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>0.9941768272932879</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0.9937304075235109</v>
+      </c>
+      <c r="CB41" t="n">
+        <v>0.002000860549371846</v>
+      </c>
+      <c r="CC41" t="inlineStr">
+        <is>
+          <t>0.9940828402366864, 0.9882352941176471, 0.9822485207100591, 0.9882352941176471, 0.9940828402366864, 0.9883720930232558, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CD41" t="inlineStr">
+        <is>
+          <t>0.9978586723768736, 0.9957264957264957, 0.9936034115138592, 0.9957264957264957, 0.9978678038379531, 0.9957081545064378, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CE41" t="n">
+        <v>0.9960310756306586</v>
+      </c>
+      <c r="CF41" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="CG41" t="n">
+        <v>0.001362236514222641</v>
+      </c>
+      <c r="CH41" t="inlineStr">
+        <is>
+          <t>0.99597075630678, 0.9919808949220714, 0.9879259661119592, 0.9919808949220714, 0.9959753220373198, 0.9920401237648468, 0.9919808949220714</t>
+        </is>
+      </c>
+      <c r="CI41" t="n">
+        <v>0.9925506932838742</v>
+      </c>
+      <c r="CJ41" t="n">
+        <v>0.9919808949220714</v>
+      </c>
+      <c r="CK41" t="n">
+        <v>0.002564808718774788</v>
+      </c>
+      <c r="CL41" t="n">
+        <v>0.9890703109370899</v>
+      </c>
+      <c r="CM41" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="CN41" t="n">
+        <v>0.003767662962286438</v>
+      </c>
+      <c r="CO41" t="inlineStr">
+        <is>
+          <t>0.9882352941176471, 0.9882352941176471, 0.9880952380952381, 0.9882352941176471, 1.0, 0.9770114942528736, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CP41" t="inlineStr">
+        <is>
+          <t>1.0, 0.9957264957264957, 0.9914893617021276, 0.9957264957264957, 0.9957446808510638, 1.0, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CQ41" t="n">
+        <v>0.9963447899618112</v>
+      </c>
+      <c r="CR41" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="CS41" t="n">
+        <v>0.00272038071549241</v>
+      </c>
+      <c r="CT41" t="n">
+        <v>0.9882925584026714</v>
+      </c>
+      <c r="CU41" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="CV41" t="n">
+        <v>0.006145598299407894</v>
+      </c>
+      <c r="CW41" t="inlineStr">
+        <is>
+          <t>1.0, 0.9882352941176471, 0.9764705882352941, 0.9882352941176471, 0.9882352941176471, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CX41" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 0.9957264957264957, 0.9957264957264957, 0.9957264957264957, 1.0, 0.9914529914529915, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CY41" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="CZ41" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="DA41" t="n">
+        <v>0.002284284118909602</v>
+      </c>
+      <c r="DB41" t="n">
+        <v>0.9899159663865547</v>
+      </c>
+      <c r="DC41" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="DD41" t="n">
+        <v>0.007516194882352237</v>
+      </c>
+      <c r="DE41" t="inlineStr">
+        <is>
+          <t>0.9998473748473748, 0.9999497234791352, 0.9992458521870287, 0.9998491704374057, 0.9994469582704877, 0.9998994469582705, 0.9997486173956763</t>
+        </is>
+      </c>
+      <c r="DF41" t="n">
+        <v>0.999712449082197</v>
+      </c>
+      <c r="DG41" t="n">
+        <v>0.9998473748473748</v>
+      </c>
+      <c r="DH41" t="n">
+        <v>0.0002442689433391249</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Logit_splashing_smote_11-dim_vae</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 11, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.06738963184824698}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.007629064741003484, 'beta_warmup_steps': 1864, 'beta_start': 0.0099049185471573, 'beta_end': 0.06163350857331332}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8904320987654321</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.793956043956044</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.7893518518518519</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.7307692307692308</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.8653198653198653</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.9318181818181818</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.9381696428571429</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.8571565986918045</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.8699404761904761</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.768595041322314</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.8230088495575221</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>3.9692561626434326, 3.5453906059265137, 3.5379912853240967, 2.690220594406128, 3.7544593811035156, 3.8590378761291504, 3.7549214363098145</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.58732533454895</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.754459381103516</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.3936478466505545</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>0.019008874893188477, 0.019000768661499023, 0.019001483917236328, 0.019998550415039062, 0.01900029182434082, 0.018032073974609375, 0.017998933792114258</t>
+        </is>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.01886299678257533</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.01900076866149902</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.0006329985043112958</v>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7924528301886793, 0.7735849056603774, 0.8301886792452831, 0.7924528301886793, 0.7735849056603774, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>0.9451127819548872, 0.8023809523809524, 0.8119195046439629, 0.8560371517027863, 0.8034055727554179, 0.8003095975232198, 0.7213622291021672</t>
+        </is>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.8200753985804848</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.8034055727554179</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.0629286066835007</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.8033842467804734</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0.06557106112049649</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>0.9565217391304348, 0.8307692307692307, 0.7931034482758621, 0.8524590163934426, 0.8253968253968255, 0.8000000000000002, 0.7619047619047619</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>0.9230769230769231, 0.7317073170731708, 0.75, 0.7999999999999999, 0.744186046511628, 0.7391304347826088, 0.6511627906976745</t>
+        </is>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.7627519303060007</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.744186046511628</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0.07706463419993148</v>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>0.939799331103679, 0.7812382739212007, 0.771551724137931, 0.8262295081967213, 0.7847914359542267, 0.7695652173913045, 0.7065337763012182</t>
+        </is>
+      </c>
+      <c r="AU42" t="n">
+        <v>0.7971013238580402</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0.7812382739212007</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.06679161834061656</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.8314507174100797</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0.8253968253968255</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0.05783909174314814</v>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>0.9705882352941176, 0.9, 0.9583333333333334, 0.9629629629629629, 0.896551724137931, 0.9230769230769231, 0.8275862068965517</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>0.9, 0.6521739130434783, 0.6206896551724138, 0.6923076923076923, 0.6666666666666666, 0.6296296296296297, 0.5833333333333334</t>
+        </is>
+      </c>
+      <c r="BC42" t="n">
+        <v>0.6778286985933162</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0.09626591296559736</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0.9198713408145457</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0.04686441318338971</v>
+      </c>
+      <c r="BI42" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.7714285714285715, 0.6764705882352942, 0.7647058823529411, 0.7647058823529411, 0.7058823529411765, 0.7058823529411765</t>
+        </is>
+      </c>
+      <c r="BJ42" t="inlineStr">
+        <is>
+          <t>0.9473684210526315, 0.8333333333333334, 0.9473684210526315, 0.9473684210526315, 0.8421052631578947, 0.8947368421052632, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK42" t="n">
+        <v>0.8784461152882204</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>0.07360488799793691</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>0.7617046818727492</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>0.08143875708629902</v>
+      </c>
+      <c r="BQ42" t="inlineStr">
+        <is>
+          <t>0.9804511278195489, 0.9, 0.9504643962848297, 0.9009287925696594, 0.9117647058823529, 0.8869969040247678, 0.8591331269349844</t>
+        </is>
+      </c>
+      <c r="BR42" t="n">
+        <v>0.9128198647880205</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>0.9009287925696594</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>0.03750628424817968</v>
+      </c>
+      <c r="BU42" t="inlineStr">
+        <is>
+          <t>0.8238993710691824, 0.8213166144200627, 0.8150470219435737, 0.8808777429467085, 0.8244514106583072, 0.8808777429467085, 0.8150470219435737</t>
+        </is>
+      </c>
+      <c r="BV42" t="inlineStr">
+        <is>
+          <t>0.8435570904381611, 0.8415062045357296, 0.8488057393246842, 0.8937838302259644, 0.8361113497723172, 0.899776613111092, 0.824834607784174</t>
+        </is>
+      </c>
+      <c r="BW42" t="n">
+        <v>0.855482205027446</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>0.8435570904381611</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>0.02705979218698977</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>0.8373595608468739</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>0.8238993710691824</v>
+      </c>
+      <c r="CB42" t="n">
+        <v>0.027745105903994</v>
+      </c>
+      <c r="CC42" t="inlineStr">
+        <is>
+          <t>0.8502673796791445, 0.8471849865951744, 0.8365650969529086, 0.902061855670103, 0.8541666666666666, 0.9005235602094241, 0.8467532467532468</t>
+        </is>
+      </c>
+      <c r="CD42" t="inlineStr">
+        <is>
+          <t>0.7862595419847327, 0.7849056603773585, 0.7870036101083033, 0.8480000000000001, 0.7795275590551181, 0.8515625, 0.766798418972332</t>
+        </is>
+      </c>
+      <c r="CE42" t="n">
+        <v>0.8005796129282636</v>
+      </c>
+      <c r="CF42" t="n">
+        <v>0.7862595419847327</v>
+      </c>
+      <c r="CG42" t="n">
+        <v>0.03177454280784311</v>
+      </c>
+      <c r="CH42" t="inlineStr">
+        <is>
+          <t>0.8182634608319386, 0.8160453234862665, 0.811784353530606, 0.8750309278350515, 0.8168471128608923, 0.8760430301047121, 0.8067758328627894</t>
+        </is>
+      </c>
+      <c r="CI42" t="n">
+        <v>0.8315414345017508</v>
+      </c>
+      <c r="CJ42" t="n">
+        <v>0.8168471128608923</v>
+      </c>
+      <c r="CK42" t="n">
+        <v>0.02805036909485266</v>
+      </c>
+      <c r="CL42" t="n">
+        <v>0.8625032560752384</v>
+      </c>
+      <c r="CM42" t="n">
+        <v>0.8502673796791445</v>
+      </c>
+      <c r="CN42" t="n">
+        <v>0.02502896035359379</v>
+      </c>
+      <c r="CO42" t="inlineStr">
+        <is>
+          <t>0.9408284023668639, 0.9404761904761905, 0.9741935483870968, 0.9615384615384616, 0.9213483146067416, 0.9772727272727273, 0.9106145251396648</t>
+        </is>
+      </c>
+      <c r="CP42" t="inlineStr">
+        <is>
+          <t>0.6912751677852349, 0.6887417218543046, 0.6646341463414634, 0.7737226277372263, 0.7021276595744681, 0.7622377622377622, 0.6928571428571428</t>
+        </is>
+      </c>
+      <c r="CQ42" t="n">
+        <v>0.710799461198229</v>
+      </c>
+      <c r="CR42" t="n">
+        <v>0.6928571428571428</v>
+      </c>
+      <c r="CS42" t="n">
+        <v>0.03779895846268833</v>
+      </c>
+      <c r="CT42" t="n">
+        <v>0.9466103099696781</v>
+      </c>
+      <c r="CU42" t="n">
+        <v>0.9408284023668639</v>
+      </c>
+      <c r="CV42" t="n">
+        <v>0.0236908402988297</v>
+      </c>
+      <c r="CW42" t="inlineStr">
+        <is>
+          <t>0.775609756097561, 0.7707317073170732, 0.7330097087378641, 0.8495145631067961, 0.7961165048543689, 0.8349514563106796, 0.7912621359223301</t>
+        </is>
+      </c>
+      <c r="CX42" t="inlineStr">
+        <is>
+          <t>0.911504424778761, 0.9122807017543859, 0.9646017699115044, 0.9380530973451328, 0.8761061946902655, 0.9646017699115044, 0.8584070796460177</t>
+        </is>
+      </c>
+      <c r="CY42" t="n">
+        <v>0.9179364340053674</v>
+      </c>
+      <c r="CZ42" t="n">
+        <v>0.9122807017543859</v>
+      </c>
+      <c r="DA42" t="n">
+        <v>0.03803543140654948</v>
+      </c>
+      <c r="DB42" t="n">
+        <v>0.7930279760495246</v>
+      </c>
+      <c r="DC42" t="n">
+        <v>0.7912621359223301</v>
+      </c>
+      <c r="DD42" t="n">
+        <v>0.03657415229541591</v>
+      </c>
+      <c r="DE42" t="inlineStr">
+        <is>
+          <t>0.914936326354414, 0.9282841249465127, 0.9184852650571356, 0.9462367901022425, 0.9334779620242288, 0.9453561302517399, 0.9153062977919064</t>
+        </is>
+      </c>
+      <c r="DF42" t="n">
+        <v>0.9288689852183113</v>
+      </c>
+      <c r="DG42" t="n">
+        <v>0.9282841249465127</v>
+      </c>
+      <c r="DH42" t="n">
+        <v>0.01242657546323508</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_smote_11-dim_vae</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 11, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.06738963184824698}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.007629064741003484, 'beta_warmup_steps': 1864, 'beta_start': 0.0099049185471573, 'beta_end': 0.06163350857331332}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9490740740740741</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.863608809860578</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.849537037037037</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.9932659932659933</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.9947916666666666</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.9947916666666666</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.9947916666666666</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.999826388888889</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.9926339285714285</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.9926339285714285</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>5.829761981964111, 5.348426103591919, 5.399703025817871, 4.442035913467407, 5.593037128448486, 5.658374547958374, 5.55912971496582</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>5.404352630887713</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>5.55912971496582</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.4199083055723075</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>0.01999974250793457, 0.020000457763671875, 0.02000117301940918, 0.019034147262573242, 0.01900005340576172, 0.02000117301940918, 0.020000934600830078</t>
+        </is>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.01971966879708426</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.02000045776367188</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.0004444369663974112</v>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8113207547169812, 0.9056603773584906, 0.9245283018867925, 0.9245283018867925, 0.8867924528301887, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8301587301587301, 0.914860681114551, 0.9411764705882353, 0.9179566563467492, 0.8885448916408669, 0.8622291021671826</t>
+        </is>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.9003278504384209</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.914860681114551</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.03949224371543408</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.897673954277728</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0.04508572798215413</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8437500000000001, 0.923076923076923, 0.9375, 0.9411764705882353, 0.9090909090909091, 0.8955223880597014</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.761904761904762, 0.8780487804878049, 0.9047619047619047, 0.8947368421052632, 0.8500000000000001, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.8649156506024286</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.055779754041979</v>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.802827380952381, 0.900562851782364, 0.9211309523809523, 0.9179566563467492, 0.8795454545454546, 0.858017604286261</t>
+        </is>
+      </c>
+      <c r="AU43" t="n">
+        <v>0.8911963190896424</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0.9005628517823639</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0.04667967977117931</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0.9174769875768558</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0.03775671362245039</v>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9310344827586207, 0.967741935483871, 1.0, 0.9411764705882353, 0.9375, 0.9090909090909091</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>1.0, 0.6666666666666666, 0.8181818181818182, 0.8260869565217391, 0.8947368421052632, 0.8095238095238095, 0.8</t>
+        </is>
+      </c>
+      <c r="BC43" t="n">
+        <v>0.8307422989998995</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0.09353306150086366</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0.947498534838226</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0.02687207676545528</v>
+      </c>
+      <c r="BI43" t="inlineStr">
+        <is>
+          <t>1.0, 0.7714285714285715, 0.8823529411764706, 0.8823529411764706, 0.9411764705882353, 0.8823529411764706, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BJ43" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8888888888888888, 0.9473684210526315, 1.0, 0.8947368421052632, 0.8947368421052632, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK43" t="n">
+        <v>0.908939014202172</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>0.04666412713038912</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>0.89171668667467</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>0.06435559222894424</v>
+      </c>
+      <c r="BQ43" t="inlineStr">
+        <is>
+          <t>0.9774436090225564, 0.9301587301587302, 0.9690402476780186, 0.9721362229102168, 0.9489164086687305, 0.9256965944272446, 0.9396284829721362</t>
+        </is>
+      </c>
+      <c r="BR43" t="n">
+        <v>0.951860042262519</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>0.9489164086687305</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>0.01954683320718267</v>
+      </c>
+      <c r="BU43" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9968652037617555, 0.9937304075235109, 0.987460815047022, 1.0, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV43" t="inlineStr">
+        <is>
+          <t>0.9931361968486941, 1.0, 0.995575221238938, 0.9931480367729186, 0.9882936678408798, 1.0, 0.9931480367729186</t>
+        </is>
+      </c>
+      <c r="BW43" t="n">
+        <v>0.9947573084963356</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>0.9931480367729186</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>0.003877163435080195</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>0.9950710750970998</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>0.9937304075235109</v>
+      </c>
+      <c r="CB43" t="n">
+        <v>0.004056194184344267</v>
+      </c>
+      <c r="CC43" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 0.9975786924939467, 0.9951456310679612, 0.9902439024390244, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CD43" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9955555555555555, 0.9911504424778761, 0.9824561403508772, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CE43" t="n">
+        <v>0.9930661461914373</v>
+      </c>
+      <c r="CF43" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="CG43" t="n">
+        <v>0.005681244862960097</v>
+      </c>
+      <c r="CH43" t="inlineStr">
+        <is>
+          <t>0.9931361968486941, 1.0, 0.9965671240247511, 0.9931480367729186, 0.9863500213949508, 1.0, 0.9931480367729186</t>
+        </is>
+      </c>
+      <c r="CI43" t="n">
+        <v>0.9946213451163191</v>
+      </c>
+      <c r="CJ43" t="n">
+        <v>0.9931480367729186</v>
+      </c>
+      <c r="CK43" t="n">
+        <v>0.00441762134938758</v>
+      </c>
+      <c r="CL43" t="n">
+        <v>0.9961765440412008</v>
+      </c>
+      <c r="CM43" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="CN43" t="n">
+        <v>0.003154081635357838</v>
+      </c>
+      <c r="CO43" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 0.9951690821256038, 0.9951456310679612, 0.9950980392156863, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CP43" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 1.0, 0.9911504424778761, 0.9739130434782609, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CQ43" t="n">
+        <v>0.9924806244159841</v>
+      </c>
+      <c r="CR43" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="CS43" t="n">
+        <v>0.00861631543198957</v>
+      </c>
+      <c r="CT43" t="n">
+        <v>0.9965257620995321</v>
+      </c>
+      <c r="CU43" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="CV43" t="n">
+        <v>0.002197395844379775</v>
+      </c>
+      <c r="CW43" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 1.0, 0.9951456310679612, 0.9854368932038835, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CX43" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY43" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ43" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA43" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB43" t="n">
+        <v>0.995835729508474</v>
+      </c>
+      <c r="DC43" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="DD43" t="n">
+        <v>0.00480507460668171</v>
+      </c>
+      <c r="DE43" t="inlineStr">
+        <is>
+          <t>0.999935247140082, 1.0, 0.9996778073717674, 0.9996778073717674, 0.9994630122862789, 1.0, 0.9997637254059627</t>
+        </is>
+      </c>
+      <c r="DF43" t="n">
+        <v>0.9997882285108368</v>
+      </c>
+      <c r="DG43" t="n">
+        <v>0.9997637254059627</v>
+      </c>
+      <c r="DH43" t="n">
+        <v>0.0001859571591833885</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Logit_no_fragmentation_smote_11-dim_vae</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 11, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.06738963184824698}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.007629064741003484, 'beta_warmup_steps': 1864, 'beta_start': 0.0099049185471573, 'beta_end': 0.06163350857331332}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5862068965517241</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6938775510204082</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9281818181818182</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.7726813497676299</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.8159090909090909</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.9347826086956522</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.7818181818181819</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.8514851485148516</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.8249158249158249</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.9113924050632911</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.7346938775510204</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.9351410985948205</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.8020203056096811</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.8524851933573336</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.7935779816513762</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.8693467336683417</v>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>3.7058489322662354, 4.799809455871582, 4.138448715209961, 3.2296526432037354, 3.779139995574951, 4.12170672416687, 4.120167016983032</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.984967640468053</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4.120167016983032</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.4496463833817112</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>0.017000436782836914, 0.017000675201416016, 0.01699972152709961, 0.017000198364257812, 0.016000986099243164, 0.01700115203857422, 0.016000032424926758</t>
+        </is>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.01671474320547921</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.01700019836425781</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.0004517214603406363</v>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7358490566037735, 0.8490566037735849, 0.7735849056603774, 0.7735849056603774, 0.8301886792452831, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>0.8974358974358974, 0.7518315018315018, 0.8516483516483516, 0.8003663003663004, 0.7316849816849818, 0.8388278388278387, 0.8974358974358974</t>
+        </is>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.824175824175824</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.8388278388278387</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.06101363818430331</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0.8090246580812618</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0.04367709178050789</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>0.7894736842105263, 0.6111111111111112, 0.75, 0.6666666666666665, 0.6000000000000001, 0.7272727272727273, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>0.8857142857142858, 0.8, 0.8918918918918919, 0.8285714285714285, 0.8421052631578947, 0.8767123287671232, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.8586727834024158</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.8767123287671232</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.03276428774981135</v>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>0.8375939849624061, 0.7055555555555556, 0.8209459459459459, 0.7476190476190475, 0.7210526315789474, 0.8019925280199253, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU44" t="n">
+        <v>0.780929389346837</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0.8019925280199253</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0.05101009418456508</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0.7031859952912585</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0.07195238132879253</v>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>0.6521739130434783, 0.5, 0.6666666666666666, 0.5454545454545454, 0.5625, 0.631578947368421, 0.6363636363636364</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>1.0, 0.9032258064516129, 0.9428571428571428, 0.9354838709677419, 0.8648648648648649, 0.9411764705882353, 1.0</t>
+        </is>
+      </c>
+      <c r="BC44" t="n">
+        <v>0.9410868793899426</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0.04507026809809384</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0.599248244128107</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0.05838738399264363</v>
+      </c>
+      <c r="BI44" t="inlineStr">
+        <is>
+          <t>1.0, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.6428571428571429, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ44" t="inlineStr">
+        <is>
+          <t>0.7948717948717948, 0.717948717948718, 0.8461538461538461, 0.7435897435897436, 0.8205128205128205, 0.8205128205128205, 0.7948717948717948</t>
+        </is>
+      </c>
+      <c r="BK44" t="n">
+        <v>0.7912087912087912</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0.7948717948717948</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>0.04208470803324561</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>0.1145405322481819</v>
+      </c>
+      <c r="BQ44" t="inlineStr">
+        <is>
+          <t>0.9623931623931624, 0.8406593406593407, 0.9578754578754579, 0.8974358974358974, 0.8974358974358975, 0.9175824175824177, 0.9761904761904762</t>
+        </is>
+      </c>
+      <c r="BR44" t="n">
+        <v>0.9213675213675214</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>0.9175824175824177</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>0.04423164949130195</v>
+      </c>
+      <c r="BU44" t="inlineStr">
+        <is>
+          <t>0.8207547169811321, 0.8683385579937304, 0.8557993730407524, 0.8652037617554859, 0.8652037617554859, 0.8620689655172413, 0.8526645768025078</t>
+        </is>
+      </c>
+      <c r="BV44" t="inlineStr">
+        <is>
+          <t>0.8591269841269842, 0.8802916038210156, 0.8642533936651584, 0.8819004524886878, 0.8631724484665662, 0.8872549019607843, 0.8733534439416792</t>
+        </is>
+      </c>
+      <c r="BW44" t="n">
+        <v>0.872764746924411</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>0.8733534439416792</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>0.01000621054418873</v>
+      </c>
+      <c r="BZ44" t="n">
+        <v>0.8557191019780479</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="CB44" t="n">
+        <v>0.01517203143470477</v>
+      </c>
+      <c r="CC44" t="inlineStr">
+        <is>
+          <t>0.7348837209302326, 0.7857142857142858, 0.7653061224489796, 0.7839195979899497, 0.7724867724867726, 0.7843137254901961, 0.7684729064039408</t>
+        </is>
+      </c>
+      <c r="CD44" t="inlineStr">
+        <is>
+          <t>0.8646080760095012, 0.9049773755656108, 0.8959276018099548, 0.9020501138952163, 0.9042316258351892, 0.8986175115207373, 0.8919540229885059</t>
+        </is>
+      </c>
+      <c r="CE44" t="n">
+        <v>0.8946237610892452</v>
+      </c>
+      <c r="CF44" t="n">
+        <v>0.8986175115207373</v>
+      </c>
+      <c r="CG44" t="n">
+        <v>0.01298558546547036</v>
+      </c>
+      <c r="CH44" t="inlineStr">
+        <is>
+          <t>0.7997458984698669, 0.8453458306399483, 0.8306168621294672, 0.842984855942583, 0.8383591991609809, 0.8414656185054668, 0.8302134646962234</t>
+        </is>
+      </c>
+      <c r="CI44" t="n">
+        <v>0.8326759613635052</v>
+      </c>
+      <c r="CJ44" t="n">
+        <v>0.8383591991609809</v>
+      </c>
+      <c r="CK44" t="n">
+        <v>0.01449654629376821</v>
+      </c>
+      <c r="CL44" t="n">
+        <v>0.7707281616377654</v>
+      </c>
+      <c r="CM44" t="n">
+        <v>0.7724867724867726</v>
+      </c>
+      <c r="CN44" t="n">
+        <v>0.01649920682053521</v>
+      </c>
+      <c r="CO44" t="inlineStr">
+        <is>
+          <t>0.6030534351145038, 0.6936936936936937, 0.6756756756756757, 0.6842105263157895, 0.7019230769230769, 0.6722689075630253, 0.6610169491525424</t>
+        </is>
+      </c>
+      <c r="CP44" t="inlineStr">
+        <is>
+          <t>0.9732620320855615, 0.9615384615384616, 0.9519230769230769, 0.9658536585365853, 0.9441860465116279, 0.975, 0.9651741293532339</t>
+        </is>
+      </c>
+      <c r="CQ44" t="n">
+        <v>0.9624196292783639</v>
+      </c>
+      <c r="CR44" t="n">
+        <v>0.9651741293532339</v>
+      </c>
+      <c r="CS44" t="n">
+        <v>0.01027215975468676</v>
+      </c>
+      <c r="CT44" t="n">
+        <v>0.6702631806340439</v>
+      </c>
+      <c r="CU44" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="CV44" t="n">
+        <v>0.03019419802198767</v>
+      </c>
+      <c r="CW44" t="inlineStr">
+        <is>
+          <t>0.9404761904761905, 0.9058823529411765, 0.8823529411764706, 0.9176470588235294, 0.8588235294117647, 0.9411764705882353, 0.9176470588235294</t>
+        </is>
+      </c>
+      <c r="CX44" t="inlineStr">
+        <is>
+          <t>0.7777777777777778, 0.8547008547008547, 0.8461538461538461, 0.8461538461538461, 0.8675213675213675, 0.8333333333333334, 0.8290598290598291</t>
+        </is>
+      </c>
+      <c r="CY44" t="n">
+        <v>0.8363858363858363</v>
+      </c>
+      <c r="CZ44" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="DA44" t="n">
+        <v>0.02670896563397723</v>
+      </c>
+      <c r="DB44" t="n">
+        <v>0.9091436574629853</v>
+      </c>
+      <c r="DC44" t="n">
+        <v>0.9176470588235294</v>
+      </c>
+      <c r="DD44" t="n">
+        <v>0.02780785676376251</v>
+      </c>
+      <c r="DE44" t="inlineStr">
+        <is>
+          <t>0.945919820919821, 0.9551030668677728, 0.9420311714429361, 0.9478129713423831, 0.9438914027149321, 0.9528406234288587, 0.9484162895927603</t>
+        </is>
+      </c>
+      <c r="DF44" t="n">
+        <v>0.9480021923299236</v>
+      </c>
+      <c r="DG44" t="n">
+        <v>0.9478129713423831</v>
+      </c>
+      <c r="DH44" t="n">
+        <v>0.004324813261167752</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smote_11-dim_vae</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 11, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.06738963184824698}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.007629064741003484, 'beta_warmup_steps': 1864, 'beta_start': 0.0099049185471573, 'beta_end': 0.06163350857331332}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9645454545454546</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.844074844074844</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.8386363636363636</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.9107142857142857</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.918918918918919</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.9932659932659933</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.9998838694692835</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.991377308094298</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.991377308094298</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.9954128440366973</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.9954128440366973</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.9954128440366973</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>5.614685773849487, 6.647863864898682, 6.030980348587036, 5.002670049667358, 5.594502210617065, 5.919543027877808, 5.898611545562744</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>5.815550974437168</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>5.898611545562744</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.4639662474142545</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>0.017999887466430664, 0.01799917221069336, 0.017001867294311523, 0.017000913619995117, 0.018000364303588867, 0.018001556396484375, 0.017999649047851562</t>
+        </is>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.01771477290562221</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0.01799964904785156</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0.0004511832699309916</v>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.8679245283018868, 0.9245283018867925, 0.9056603773584906, 0.9622641509433962, 0.9433962264150944, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>0.7897435897435897, 0.8415750915750916, 0.88003663003663, 0.9358974358974359, 0.9285714285714286, 0.9157509157509157, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI45" t="n">
+        <v>0.8881998953427527</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.9157509157509157</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0.05072857269899758</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0.9061595288010382</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0.04631436850920789</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>0.6875, 0.7586206896551724, 0.8461538461538461, 0.8484848484848484, 0.923076923076923, 0.888888888888889, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>0.868421052631579, 0.9090909090909091, 0.9500000000000001, 0.9315068493150686, 0.975, 0.9620253164556962, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0.9347732212208406</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0.0334327147196812</v>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>0.7779605263157895, 0.8338557993730407, 0.8980769230769231, 0.8899958488999584, 0.9490384615384615, 0.9254571026722926, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU45" t="n">
+        <v>0.8830574579623021</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0.8980769230769231</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0.05407032757865034</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0.8313416947037637</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0.8484848484848484</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0.07508752092449582</v>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>0.6470588235294118, 0.7333333333333333, 0.9166666666666666, 0.7368421052631579, 1.0, 0.9230769230769231, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.9210526315789473, 0.926829268292683, 1.0, 0.9512195121951219, 0.95, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC45" t="n">
+        <v>0.9448523252759452</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0.03293964174065412</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0.8242111216956418</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0.1174955371682005</v>
+      </c>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.7857142857142857, 1.0, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.8974358974358975, 0.9743589743589743, 0.8717948717948718, 1.0, 0.9743589743589743, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK45" t="n">
+        <v>0.9267399267399268</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>0.05383493940182808</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>0.8496598639455781</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>0.08506394031205762</v>
+      </c>
+      <c r="BQ45" t="inlineStr">
+        <is>
+          <t>0.9401709401709402, 0.9175824175824177, 0.9853479853479854, 0.967032967032967, 0.989010989010989, 0.9578754578754579, 0.9706959706959707</t>
+        </is>
+      </c>
+      <c r="BR45" t="n">
+        <v>0.9611023896738183</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>0.967032967032967</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>0.0234108461101701</v>
+      </c>
+      <c r="BU45" t="inlineStr">
+        <is>
+          <t>1.0, 0.9905956112852664, 0.9968652037617555, 0.9905956112852664, 0.9937304075235109, 0.9968652037617555, 0.9905956112852664</t>
+        </is>
+      </c>
+      <c r="BV45" t="inlineStr">
+        <is>
+          <t>1.0, 0.9898441427853193, 0.9941176470588236, 0.9898441427853193, 0.9919808949220714, 0.9978632478632479, 0.986098541980895</t>
+        </is>
+      </c>
+      <c r="BW45" t="n">
+        <v>0.9928212310565252</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>0.9919808949220714</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>0.004508154101968339</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>0.9941782355575459</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>0.9937304075235109</v>
+      </c>
+      <c r="CB45" t="n">
+        <v>0.003526201466194291</v>
+      </c>
+      <c r="CC45" t="inlineStr">
+        <is>
+          <t>1.0, 0.9824561403508771, 0.9940828402366864, 0.9824561403508771, 0.9882352941176471, 0.9941520467836257, 0.9822485207100591</t>
+        </is>
+      </c>
+      <c r="CD45" t="inlineStr">
+        <is>
+          <t>1.0, 0.9935760171306209, 0.9978678038379531, 0.9935760171306209, 0.9957264957264957, 0.9978586723768736, 0.9936034115138592</t>
+        </is>
+      </c>
+      <c r="CE45" t="n">
+        <v>0.9960297739594891</v>
+      </c>
+      <c r="CF45" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="CG45" t="n">
+        <v>0.002405558314243849</v>
+      </c>
+      <c r="CH45" t="inlineStr">
+        <is>
+          <t>1.0, 0.988016078740749, 0.9959753220373198, 0.988016078740749, 0.9919808949220714, 0.9960053595802496, 0.9879259661119592</t>
+        </is>
+      </c>
+      <c r="CI45" t="n">
+        <v>0.9925599571618712</v>
+      </c>
+      <c r="CJ45" t="n">
+        <v>0.9919808949220714</v>
+      </c>
+      <c r="CK45" t="n">
+        <v>0.004503849160603997</v>
+      </c>
+      <c r="CL45" t="n">
+        <v>0.9890901403642534</v>
+      </c>
+      <c r="CM45" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="CN45" t="n">
+        <v>0.006602309334503611</v>
+      </c>
+      <c r="CO45" t="inlineStr">
+        <is>
+          <t>1.0, 0.9767441860465116, 1.0, 0.9767441860465116, 0.9882352941176471, 0.9883720930232558, 0.9880952380952381</t>
+        </is>
+      </c>
+      <c r="CP45" t="inlineStr">
+        <is>
+          <t>1.0, 0.9957081545064378, 0.9957446808510638, 0.9957081545064378, 0.9957264957264957, 1.0, 0.9914893617021276</t>
+        </is>
+      </c>
+      <c r="CQ45" t="n">
+        <v>0.9963395496132232</v>
+      </c>
+      <c r="CR45" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="CS45" t="n">
+        <v>0.00272158410581086</v>
+      </c>
+      <c r="CT45" t="n">
+        <v>0.988312999618452</v>
+      </c>
+      <c r="CU45" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="CV45" t="n">
+        <v>0.00879044774593073</v>
+      </c>
+      <c r="CW45" t="inlineStr">
+        <is>
+          <t>1.0, 0.9882352941176471, 0.9882352941176471, 0.9882352941176471, 0.9882352941176471, 1.0, 0.9764705882352941</t>
+        </is>
+      </c>
+      <c r="CX45" t="inlineStr">
+        <is>
+          <t>1.0, 0.9914529914529915, 1.0, 0.9914529914529915, 0.9957264957264957, 0.9957264957264957, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CY45" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="CZ45" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="DA45" t="n">
+        <v>0.003230465581275435</v>
+      </c>
+      <c r="DB45" t="n">
+        <v>0.9899159663865547</v>
+      </c>
+      <c r="DC45" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="DD45" t="n">
+        <v>0.007516194882352237</v>
+      </c>
+      <c r="DE45" t="inlineStr">
+        <is>
+          <t>0.9999999999999999, 0.9997486173956761, 0.9996480643539467, 0.999798893916541, 0.9996983408748115, 1.0, 0.9994469582704877</t>
+        </is>
+      </c>
+      <c r="DF45" t="n">
+        <v>0.9997629821159233</v>
+      </c>
+      <c r="DG45" t="n">
+        <v>0.9997486173956761</v>
+      </c>
+      <c r="DH45" t="n">
+        <v>0.0001817009357275317</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Logit_splashing_smote_12-dim_vae</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 12, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.05274315992660307}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.009731859118290219, 'beta_warmup_steps': 1919, 'beta_start': 0.0027332101767241434, 'beta_end': 0.06536791087939318}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.8865740740740741</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7751124437781109</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.7847222222222222</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.8585858585858586</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.9464285714285714</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.828125</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.9338541666666668</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.8519230769230769</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.8712053571428571</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>3.0529699325561523, 3.6639440059661865, 3.254997491836548, 2.9567606449127197, 3.4437432289123535, 2.4640209674835205, 3.070528745651245</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.129566431045532</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.070528745651245</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.3549978832076909</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>0.018001794815063477, 0.018000364303588867, 0.01800060272216797, 0.017999887466430664, 0.017999887466430664, 0.018001556396484375, 0.01800060272216797</t>
+        </is>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.018000670841762</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.01800060272216797</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>6.946862784239611e-07</v>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.8490566037735849, 0.7547169811320755, 0.7924528301886793, 0.8490566037735849, 0.7735849056603774, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>0.8639097744360902, 0.8587301587301588, 0.7623839009287926, 0.8150154798761611, 0.8359133126934984, 0.8003095975232198, 0.8707430340557275</t>
+        </is>
+      </c>
+      <c r="AI46" t="n">
+        <v>0.8295721797490926</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0.8359133126934984</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.03654149969370745</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0.8197564140960367</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0.04182394673055981</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>0.8985507246376812, 0.8787878787878788, 0.7936507936507937, 0.819672131147541, 0.8823529411764706, 0.8000000000000002, 0.8709677419354839</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>0.8205128205128205, 0.7999999999999999, 0.6976744186046512, 0.7555555555555555, 0.7894736842105263, 0.7391304347826088, 0.8181818181818181</t>
+        </is>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0.7743612474068543</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0.04210815228124831</v>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>0.8595317725752508, 0.8393939393939394, 0.7456626061277225, 0.7876138433515483, 0.8359133126934984, 0.7695652173913045, 0.8445747800586509</t>
+        </is>
+      </c>
+      <c r="AU46" t="n">
+        <v>0.8117507816559878</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0.8359133126934984</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0.04042324403452887</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0.8491403159051213</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0.04011076293163934</v>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>0.9117647058823529, 0.9354838709677419, 0.8620689655172413, 0.9259259259259259, 0.8823529411764706, 0.9230769230769231, 0.9642857142857143</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>0.8, 0.7272727272727273, 0.625, 0.6538461538461539, 0.7894736842105263, 0.6296296296296297, 0.72</t>
+        </is>
+      </c>
+      <c r="BC46" t="n">
+        <v>0.7064603135655767</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0.067150533239447</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0.9149941495474815</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0.03142172791438756</v>
+      </c>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>0.8857142857142857, 0.8285714285714286, 0.7352941176470589, 0.7352941176470589, 0.8823529411764706, 0.7058823529411765, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="BJ46" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.8888888888888888, 0.7894736842105263, 0.8947368421052632, 0.7894736842105263, 0.8947368421052632, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="BK46" t="n">
+        <v>0.8638262322472848</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>0.05483321330466812</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>0.7953181272509003</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>0.06767386991575898</v>
+      </c>
+      <c r="BQ46" t="inlineStr">
+        <is>
+          <t>0.956390977443609, 0.9365079365079365, 0.8962848297213623, 0.8839009287925697, 0.9349845201238391, 0.8978328173374612, 0.9040247678018576</t>
+        </is>
+      </c>
+      <c r="BR46" t="n">
+        <v>0.915703825389805</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>0.9040247678018576</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>0.02479716432747593</v>
+      </c>
+      <c r="BU46" t="inlineStr">
+        <is>
+          <t>0.8238993710691824, 0.8432601880877743, 0.7962382445141066, 0.8244514106583072, 0.799373040752351, 0.8338557993730408, 0.8432601880877743</t>
+        </is>
+      </c>
+      <c r="BV46" t="inlineStr">
+        <is>
+          <t>0.8475285991797972, 0.8527385537013265, 0.8082739066930149, 0.8401065383624022, 0.8047083082739066, 0.8553784689406306, 0.8546696451585187</t>
+        </is>
+      </c>
+      <c r="BW46" t="n">
+        <v>0.8376291457585138</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>0.8475285991797972</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>0.02029552925801852</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>0.823476891791791</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>0.8244514106583072</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>0.01778662042684287</v>
+      </c>
+      <c r="CC46" t="inlineStr">
+        <is>
+          <t>0.8486486486486488, 0.8704663212435233, 0.8293963254593176, 0.8526315789473684, 0.8350515463917526, 0.8586666666666666, 0.8704663212435233</t>
+        </is>
+      </c>
+      <c r="CD46" t="inlineStr">
+        <is>
+          <t>0.7894736842105262, 0.8015873015873015, 0.7470817120622569, 0.7829457364341085, 0.7439999999999999, 0.7984790874524714, 0.8015873015873016</t>
+        </is>
+      </c>
+      <c r="CE46" t="n">
+        <v>0.7807364033334236</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>0.7894736842105262</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>0.02313854409558755</v>
+      </c>
+      <c r="CH46" t="inlineStr">
+        <is>
+          <t>0.8190611664295875, 0.8360268114154124, 0.7882390187607873, 0.8177886576907385, 0.7895257731958762, 0.8285728770595691, 0.8360268114154125</t>
+        </is>
+      </c>
+      <c r="CI46" t="n">
+        <v>0.8164630165667691</v>
+      </c>
+      <c r="CJ46" t="n">
+        <v>0.8190611664295875</v>
+      </c>
+      <c r="CK46" t="n">
+        <v>0.01868096700842362</v>
+      </c>
+      <c r="CL46" t="n">
+        <v>0.8521896298001143</v>
+      </c>
+      <c r="CM46" t="n">
+        <v>0.8526315789473684</v>
+      </c>
+      <c r="CN46" t="n">
+        <v>0.01481316691833785</v>
+      </c>
+      <c r="CO46" t="inlineStr">
+        <is>
+          <t>0.9515151515151515, 0.9281767955801105, 0.9028571428571428, 0.9310344827586207, 0.8901098901098901, 0.9526627218934911, 0.9333333333333333</t>
+        </is>
+      </c>
+      <c r="CP46" t="inlineStr">
+        <is>
+          <t>0.6862745098039216, 0.7318840579710145, 0.6666666666666666, 0.696551724137931, 0.6788321167883211, 0.7, 0.7266187050359713</t>
+        </is>
+      </c>
+      <c r="CQ46" t="n">
+        <v>0.6981182543434036</v>
+      </c>
+      <c r="CR46" t="n">
+        <v>0.696551724137931</v>
+      </c>
+      <c r="CS46" t="n">
+        <v>0.02223199728125525</v>
+      </c>
+      <c r="CT46" t="n">
+        <v>0.9270985025782486</v>
+      </c>
+      <c r="CU46" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CV46" t="n">
+        <v>0.02158382594937679</v>
+      </c>
+      <c r="CW46" t="inlineStr">
+        <is>
+          <t>0.7658536585365854, 0.8195121951219512, 0.7669902912621359, 0.7864077669902912, 0.7864077669902912, 0.7815533980582524, 0.8155339805825242</t>
+        </is>
+      </c>
+      <c r="CX46" t="inlineStr">
+        <is>
+          <t>0.9292035398230089, 0.8859649122807017, 0.8495575221238938, 0.8938053097345132, 0.8230088495575221, 0.9292035398230089, 0.8938053097345132</t>
+        </is>
+      </c>
+      <c r="CY46" t="n">
+        <v>0.8863641404395944</v>
+      </c>
+      <c r="CZ46" t="n">
+        <v>0.8938053097345132</v>
+      </c>
+      <c r="DA46" t="n">
+        <v>0.03615433129106226</v>
+      </c>
+      <c r="DB46" t="n">
+        <v>0.7888941510774331</v>
+      </c>
+      <c r="DC46" t="n">
+        <v>0.7864077669902912</v>
+      </c>
+      <c r="DD46" t="n">
+        <v>0.01972684673611652</v>
+      </c>
+      <c r="DE46" t="inlineStr">
+        <is>
+          <t>0.911439671918843, 0.9221223791185281, 0.9136738551421943, 0.9255305438611565, 0.9134590600567059, 0.9344015808918291, 0.9241558553140304</t>
+        </is>
+      </c>
+      <c r="DF46" t="n">
+        <v>0.9206832780433267</v>
+      </c>
+      <c r="DG46" t="n">
+        <v>0.9221223791185281</v>
+      </c>
+      <c r="DH46" t="n">
+        <v>0.007677268979334033</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_smote_12-dim_vae</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 12, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.05274315992660307}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.009731859118290219, 'beta_warmup_steps': 1919, 'beta_start': 0.0027332101767241434, 'beta_end': 0.06536791087939318}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'init_volume_fraction', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.910891089108911</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.9544753086419754</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.863608809860578</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.849537037037037</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.9898989898989899</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.9846153846153847</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.9922480620155039</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.9997767857142857</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.9888776541961577</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.9857142857142858</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.9855072463768115</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>4.958646297454834, 5.423922538757324, 4.955955743789673, 4.675980806350708, 5.136261463165283, 4.196746587753296, 4.751969575881958</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.871354716164725</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>4.955955743789673</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.358130830141642</v>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>0.019112586975097656, 0.017000675201416016, 0.018001317977905273, 0.020192861557006836, 0.019998788833618164, 0.018001794815063477, 0.018999099731445312</t>
+        </is>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.01875816072736467</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.01899909973144531</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.001070036705110824</v>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8679245283018868, 0.9056603773584906, 0.9245283018867925, 0.9245283018867925, 0.9245283018867925, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.873015873015873, 0.914860681114551, 0.9411764705882353, 0.9179566563467492, 0.9295665634674922, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AI47" t="n">
+        <v>0.9106519800902817</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0.9179566563467492</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.02397040836829468</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0.9112009583707698</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0.02431139122215856</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>0.958904109589041, 0.8955223880597014, 0.923076923076923, 0.9375, 0.9411764705882353, 0.9393939393939394, 0.9117647058823528</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>0.9142857142857143, 0.8205128205128205, 0.8780487804878049, 0.9047619047619047, 0.8947368421052632, 0.9, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0.8792073321873433</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0.03246972491454433</v>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>0.9365949119373776, 0.858017604286261, 0.900562851782364, 0.9211309523809523, 0.9179566563467492, 0.9196969696969697, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AU47" t="n">
+        <v>0.9044135615643996</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0.9179566563467492</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0.02578646782971555</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0.9296197909414562</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0.01954118691208157</v>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.9375, 0.967741935483871, 1.0, 0.9411764705882353, 0.96875, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>1.0, 0.7619047619047619, 0.8181818181818182, 0.8260869565217391, 0.8947368421052632, 0.8571428571428571, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BC47" t="n">
+        <v>0.8571654998591905</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0.06928236522641133</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0.949712249076201</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>0.02853507039367077</v>
+      </c>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 0.8823529411764706, 0.8823529411764706, 0.9411764705882353, 0.9117647058823529, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ47" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.8888888888888888, 0.9473684210526315, 1.0, 0.8947368421052632, 0.9473684210526315, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK47" t="n">
+        <v>0.908939014202172</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>0.05448846736548148</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>0.9123649459783915</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>0.04368989288133938</v>
+      </c>
+      <c r="BQ47" t="inlineStr">
+        <is>
+          <t>0.98796992481203, 0.9380952380952381, 0.956656346749226, 0.9814241486068112, 0.9504643962848298, 0.9520123839009288, 0.9226006191950464</t>
+        </is>
+      </c>
+      <c r="BR47" t="n">
+        <v>0.9556032939491585</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>0.9520123839009288</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>0.02121467050938829</v>
+      </c>
+      <c r="BU47" t="inlineStr">
+        <is>
+          <t>0.9905660377358491, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 1.0, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV47" t="inlineStr">
+        <is>
+          <t>0.9906971724584502, 1.0, 0.995575221238938, 0.995575221238938, 0.9931480367729186, 1.0, 0.9931480367729186</t>
+        </is>
+      </c>
+      <c r="BW47" t="n">
+        <v>0.9954490983545947</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>0.003265048546215223</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>0.9959653229009117</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB47" t="n">
+        <v>0.003236373267744341</v>
+      </c>
+      <c r="CC47" t="inlineStr">
+        <is>
+          <t>0.9926650366748165, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9951456310679612, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CD47" t="inlineStr">
+        <is>
+          <t>0.9867841409691629, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CE47" t="n">
+        <v>0.9943137338622894</v>
+      </c>
+      <c r="CF47" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG47" t="n">
+        <v>0.004542797774108394</v>
+      </c>
+      <c r="CH47" t="inlineStr">
+        <is>
+          <t>0.9897245888219897, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9931480367729186, 1.0, 0.9931480367729186</t>
+        </is>
+      </c>
+      <c r="CI47" t="n">
+        <v>0.9955935586310469</v>
+      </c>
+      <c r="CJ47" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK47" t="n">
+        <v>0.003528153526876369</v>
+      </c>
+      <c r="CL47" t="n">
+        <v>0.9968733833998046</v>
+      </c>
+      <c r="CM47" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN47" t="n">
+        <v>0.002513586594145977</v>
+      </c>
+      <c r="CO47" t="inlineStr">
+        <is>
+          <t>0.9950980392156863, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951456310679612, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CP47" t="inlineStr">
+        <is>
+          <t>0.9824561403508771, 1.0, 1.0, 1.0, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CQ47" t="n">
+        <v>0.9949652893295184</v>
+      </c>
+      <c r="CR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS47" t="n">
+        <v>0.006402880683329265</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>0.9965324950861166</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV47" t="n">
+        <v>0.002193152255522364</v>
+      </c>
+      <c r="CW47" t="inlineStr">
+        <is>
+          <t>0.9902439024390244, 1.0, 1.0, 1.0, 0.9951456310679612, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CX47" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY47" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ47" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA47" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB47" t="n">
+        <v>0.9972193092249925</v>
+      </c>
+      <c r="DC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD47" t="n">
+        <v>0.003549357019688316</v>
+      </c>
+      <c r="DE47" t="inlineStr">
+        <is>
+          <t>0.9996330671271314, 1.0, 0.9999355614743535, 0.9998066844230604, 0.9996348483546696, 1.0, 0.999720766388865</t>
+        </is>
+      </c>
+      <c r="DF47" t="n">
+        <v>0.9998187039668686</v>
+      </c>
+      <c r="DG47" t="n">
+        <v>0.9998066844230604</v>
+      </c>
+      <c r="DH47" t="n">
+        <v>0.0001499487252064034</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Logit_no_fragmentation_smote_12-dim_vae</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'estimator': 'StatsModelsEstimator', 'estimator_params': {'model_class': 'Logit', 'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 12, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.05274315992660307}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.009731859118290219, 'beta_warmup_steps': 1919, 'beta_start': 0.0027332101767241434, 'beta_end': 0.06536791087939318}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.7450980392156863</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9345454545454546</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.8068924539512774</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.865909090909091</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.9772727272727273</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.7818181818181819</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.8619528619528619</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.6637931034482759</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.9746835443037974</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.7897435897435898</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.9563349204505864</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.8434933487565067</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.897892230867495</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.988950276243094</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.8211009174311926</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.8972431077694236</v>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>3.362372875213623, 2.5162501335144043, 3.3388171195983887, 3.3290417194366455, 3.367251396179199, 3.7820098400115967, 2.853501558303833</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.22132066317967</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.338817119598389</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.3804862391572337</v>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>0.017998695373535156, 0.01600027084350586, 0.017000198364257812, 0.016000747680664062, 0.015998125076293945, 0.016000032424926758, 0.015999555587768555</t>
+        </is>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.01642823219299316</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0.01600027084350586</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0.0007281586005142199</v>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7735849056603774, 0.8679245283018868, 0.8679245283018868, 0.7924528301886793, 0.8490566037735849, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>0.8897435897435897, 0.8003663003663004, 0.8644688644688645, 0.9102564102564102, 0.7673992673992673, 0.8287545787545787, 0.9102564102564102</t>
+        </is>
+      </c>
+      <c r="AI48" t="n">
+        <v>0.8530350601779172</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0.8644688644688645</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0.05171880409085707</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0.8413197564140962</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0.03780254172341461</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>0.8, 0.6666666666666665, 0.7741935483870968, 0.8, 0.6451612903225806, 0.7333333333333334, 0.8</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>0.9041095890410958, 0.8285714285714285, 0.9066666666666667, 0.9014084507042254, 0.8533333333333333, 0.8947368421052632, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.8843192515894626</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0.9014084507042254</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0.02841432979383783</v>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>0.8520547945205479, 0.7476190476190475, 0.8404301075268817, 0.8507042253521127, 0.749247311827957, 0.8140350877192983, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU48" t="n">
+        <v>0.8149706857025654</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0.8404301075268817</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0.04380780323152649</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0.7456221198156683</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0.06113748465344168</v>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>0.7, 0.5454545454545454, 0.7058823529411765, 0.6666666666666666, 0.5882352941176471, 0.6875, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>0.9705882352941176, 0.9354838709677419, 0.9444444444444444, 1.0, 0.8888888888888888, 0.918918918918919, 1.0</t>
+        </is>
+      </c>
+      <c r="BC48" t="n">
+        <v>0.9511891940734446</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0.03846363747885059</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0.651486503692386</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>0.05645960127390039</v>
+      </c>
+      <c r="BI48" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.8571428571428571, 0.8571428571428571, 1.0, 0.7142857142857143, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ48" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.7435897435897436, 0.8717948717948718, 0.8205128205128205, 0.8205128205128205, 0.8717948717948718, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="BK48" t="n">
+        <v>0.8278388278388278</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>0.0404591978651548</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>0.8782312925170067</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>0.09929642816815043</v>
+      </c>
+      <c r="BQ48" t="inlineStr">
+        <is>
+          <t>0.9435897435897436, 0.8846153846153846, 0.9633699633699634, 0.923076923076923, 0.9010989010989011, 0.924908424908425, 0.9633699633699633</t>
+        </is>
+      </c>
+      <c r="BR48" t="n">
+        <v>0.9291470434327577</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>0.924908424908425</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>0.02771174907976169</v>
+      </c>
+      <c r="BU48" t="inlineStr">
+        <is>
+          <t>0.8490566037735849, 0.8683385579937304, 0.8652037617554859, 0.8495297805642633, 0.8746081504702194, 0.8840125391849529, 0.8181818181818182</t>
+        </is>
+      </c>
+      <c r="BV48" t="inlineStr">
+        <is>
+          <t>0.8821733821733821, 0.8877828054298642, 0.8893916540975364, 0.8749622926093514, 0.8770739064856712, 0.9059577677224735, 0.8573403720462545</t>
+        </is>
+      </c>
+      <c r="BW48" t="n">
+        <v>0.8820974543663619</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>0.8821733821733821</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>0.01385593517249208</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>0.8584187445605794</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>0.8652037617554859</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>0.02016805093394201</v>
+      </c>
+      <c r="CC48" t="inlineStr">
+        <is>
+          <t>0.7692307692307692, 0.79, 0.7881773399014779, 0.766990291262136, 0.7894736842105262, 0.814070351758794, 0.7339449541284403</t>
+        </is>
+      </c>
+      <c r="CD48" t="inlineStr">
+        <is>
+          <t>0.8878504672897196, 0.9041095890410958, 0.9011494252873563, 0.8888888888888888, 0.9107142857142857, 0.9157175398633256, 0.861904761904762</t>
+        </is>
+      </c>
+      <c r="CE48" t="n">
+        <v>0.8957621368556333</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>0.9011494252873563</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>0.01680410490166158</v>
+      </c>
+      <c r="CH48" t="inlineStr">
+        <is>
+          <t>0.8285406182602444, 0.847054794520548, 0.8446633825944171, 0.8279395900755124, 0.850093984962406, 0.8648939458110598, 0.7979248580166012</t>
+        </is>
+      </c>
+      <c r="CI48" t="n">
+        <v>0.8373015963201127</v>
+      </c>
+      <c r="CJ48" t="n">
+        <v>0.8446633825944171</v>
+      </c>
+      <c r="CK48" t="n">
+        <v>0.01996150991570747</v>
+      </c>
+      <c r="CL48" t="n">
+        <v>0.778841055784592</v>
+      </c>
+      <c r="CM48" t="n">
+        <v>0.7881773399014779</v>
+      </c>
+      <c r="CN48" t="n">
+        <v>0.02334310081779599</v>
+      </c>
+      <c r="CO48" t="inlineStr">
+        <is>
+          <t>0.6451612903225806, 0.6869565217391305, 0.6779661016949152, 0.6528925619834711, 0.7142857142857143, 0.7105263157894737, 0.6015037593984962</t>
+        </is>
+      </c>
+      <c r="CP48" t="inlineStr">
+        <is>
+          <t>0.979381443298969, 0.9705882352941176, 0.9751243781094527, 0.9696969696969697, 0.9532710280373832, 0.9804878048780488, 0.9731182795698925</t>
+        </is>
+      </c>
+      <c r="CQ48" t="n">
+        <v>0.9716668769835477</v>
+      </c>
+      <c r="CR48" t="n">
+        <v>0.9731182795698925</v>
+      </c>
+      <c r="CS48" t="n">
+        <v>0.008407780808957308</v>
+      </c>
+      <c r="CT48" t="n">
+        <v>0.6698988950305402</v>
+      </c>
+      <c r="CU48" t="n">
+        <v>0.6779661016949152</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>0.03694760483621378</v>
+      </c>
+      <c r="CW48" t="inlineStr">
+        <is>
+          <t>0.9523809523809523, 0.9294117647058824, 0.9411764705882353, 0.9294117647058824, 0.8823529411764706, 0.9529411764705882, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="CX48" t="inlineStr">
+        <is>
+          <t>0.811965811965812, 0.8461538461538461, 0.8376068376068376, 0.8205128205128205, 0.8717948717948718, 0.8589743589743589, 0.7735042735042735</t>
+        </is>
+      </c>
+      <c r="CY48" t="n">
+        <v>0.8315018315018313</v>
+      </c>
+      <c r="CZ48" t="n">
+        <v>0.8376068376068376</v>
+      </c>
+      <c r="DA48" t="n">
+        <v>0.03046391929151317</v>
+      </c>
+      <c r="DB48" t="n">
+        <v>0.9326930772308923</v>
+      </c>
+      <c r="DC48" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="DD48" t="n">
+        <v>0.02235172475993427</v>
+      </c>
+      <c r="DE48" t="inlineStr">
+        <is>
+          <t>0.9572140822140822, 0.956913021618904, 0.9440925087983911, 0.9443941679235797, 0.9519356460532932, 0.9549019607843138, 0.9310206133735546</t>
+        </is>
+      </c>
+      <c r="DF48" t="n">
+        <v>0.9486388572523028</v>
+      </c>
+      <c r="DG48" t="n">
+        <v>0.9519356460532932</v>
+      </c>
+      <c r="DH48" t="n">
+        <v>0.008792697867260509</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smote_12-dim_vae</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'dim_transformer': 'BetaVAEncoder', 'dim_transformer_params': {'VAE_params': {'latent_dim': 12, 'hidden_dim': 64, 'normalization': 'batch', 'activation': 'LeakyReLU', 'negative_slope': 0.05274315992660307}, 'verbose': False, 'early_stopping': True, 'early_stopping_patience': 10, 'max_epochs': 500, 'learning_rate': 0.009731859118290219, 'beta_warmup_steps': 1919, 'beta_start': 0.0027332101767241434, 'beta_end': 0.06536791087939318}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sign_particle_droplet_diameter_ratio'), 'log_features': ('relative_roughness', 'sedimentation_Re', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction', 'init_volume_fraction'), 'std_features': ('sedimentation_Re', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'relative_roughness', 'Re', 'We', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': None, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.9700000000000001</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8977272727272727</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.8977272727272727</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.9937106918238994</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.9957059206245933</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.9977064220183487</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9954128440366973</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.9977011494252873</v>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>5.1960484981536865, 4.339100360870361, 5.147062063217163, 5.110127925872803, 5.136470079421997, 5.655794858932495, 4.68699836730957</t>
+        </is>
+      </c>
+      <c r="Z49" t="n">
+        <v>5.038800307682583</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>5.136470079421997</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.3863938611678702</v>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>0.01699995994567871, 0.017001628875732422, 0.01700115203857422, 0.018001794815063477, 0.017001628875732422, 0.017001628875732422, 0.016000986099243164</t>
+        </is>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.01700125421796526</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0.01700162887573242</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.0005347389085819898</v>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.8301886792452831, 0.9056603773584906, 0.8301886792452831, 0.9433962264150944, 0.9433962264150944, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>0.7897435897435897, 0.8159340659340659, 0.8443223443223443, 0.8159340659340659, 0.8928571428571428, 0.9157509157509157, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="AI49" t="n">
+        <v>0.8604657247514391</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.8443223443223443</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.05493174691194117</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0.8845961864829789</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.05310764928685688</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>0.6875, 0.7096774193548386, 0.8, 0.7096774193548386, 0.88, 0.888888888888889, 0.8750000000000001</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>0.868421052631579, 0.8799999999999999, 0.9382716049382716, 0.8799999999999999, 0.962962962962963, 0.9620253164556962, 0.945945945945946</t>
+        </is>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0.9196609832763508</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0.9382716049382716</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0.03869029105430998</v>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>0.7779605263157895, 0.7948387096774192, 0.8691358024691358, 0.7948387096774192, 0.9214814814814816, 0.9254571026722926, 0.910472972972973</t>
+        </is>
+      </c>
+      <c r="AU49" t="n">
+        <v>0.8563121864666444</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0.8691358024691358</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>0.06073696417184789</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0.792963389656938</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0.08328284381797457</v>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>0.6470588235294118, 0.6470588235294118, 0.9090909090909091, 0.6470588235294118, 1.0, 0.9230769230769231, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.9166666666666666, 0.9047619047619048, 0.9166666666666666, 0.9285714285714286, 0.95, 1.0</t>
+        </is>
+      </c>
+      <c r="BC49" t="n">
+        <v>0.9297940797940798</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0.03326621818170599</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>0.7930174400762635</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>0.1400889003351904</v>
+      </c>
+      <c r="BI49" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.7142857142857143, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ49" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.8461538461538461, 0.9743589743589743, 0.8461538461538461, 1.0, 0.9743589743589743, 0.8974358974358975</t>
+        </is>
+      </c>
+      <c r="BK49" t="n">
+        <v>0.9120879120879122</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>0.06407639444884945</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>0.808843537414966</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>0.08873836113806982</v>
+      </c>
+      <c r="BQ49" t="inlineStr">
+        <is>
+          <t>0.9435897435897436, 0.9065934065934066, 0.9542124542124543, 0.945054945054945, 0.9780219780219781, 0.9578754578754578, 0.9615384615384616</t>
+        </is>
+      </c>
+      <c r="BR49" t="n">
+        <v>0.9495552066980639</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>0.9542124542124543</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>0.0205162909953075</v>
+      </c>
+      <c r="BU49" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 0.9968652037617555, 0.9905956112852664, 0.987460815047022, 0.9905956112852664, 1.0, 0.987460815047022</t>
+        </is>
+      </c>
+      <c r="BV49" t="inlineStr">
+        <is>
+          <t>0.9978632478632479, 0.9941176470588236, 0.986098541980895, 0.9877073906485672, 0.9898441427853193, 1.0, 0.9802161890397185</t>
+        </is>
+      </c>
+      <c r="BW49" t="n">
+        <v>0.9908353084823673</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>0.9898441427853193</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>0.006437903198201757</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>0.9928333431911832</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>0.9905956112852664</v>
+      </c>
+      <c r="CB49" t="n">
+        <v>0.00465274697428263</v>
+      </c>
+      <c r="CC49" t="inlineStr">
+        <is>
+          <t>0.9940828402366864, 0.9940828402366864, 0.9822485207100591, 0.9767441860465116, 0.9824561403508771, 1.0, 0.9761904761904762</t>
+        </is>
+      </c>
+      <c r="CD49" t="inlineStr">
+        <is>
+          <t>0.9978586723768736, 0.9978678038379531, 0.9936034115138592, 0.9914163090128757, 0.9935760171306209, 1.0, 0.9914893617021276</t>
+        </is>
+      </c>
+      <c r="CE49" t="n">
+        <v>0.9951159393677587</v>
+      </c>
+      <c r="CF49" t="n">
+        <v>0.9936034115138592</v>
+      </c>
+      <c r="CG49" t="n">
+        <v>0.003172376801928427</v>
+      </c>
+      <c r="CH49" t="inlineStr">
+        <is>
+          <t>0.99597075630678, 0.9959753220373198, 0.9879259661119592, 0.9840802475296937, 0.988016078740749, 1.0, 0.9838399189463019</t>
+        </is>
+      </c>
+      <c r="CI49" t="n">
+        <v>0.9908297556675433</v>
+      </c>
+      <c r="CJ49" t="n">
+        <v>0.988016078740749</v>
+      </c>
+      <c r="CK49" t="n">
+        <v>0.005949340552644329</v>
+      </c>
+      <c r="CL49" t="n">
+        <v>0.9865435719673281</v>
+      </c>
+      <c r="CM49" t="n">
+        <v>0.9824561403508771</v>
+      </c>
+      <c r="CN49" t="n">
+        <v>0.008727016398883578</v>
+      </c>
+      <c r="CO49" t="inlineStr">
+        <is>
+          <t>0.9882352941176471, 1.0, 0.9880952380952381, 0.9655172413793104, 0.9767441860465116, 1.0, 0.9879518072289156</t>
+        </is>
+      </c>
+      <c r="CP49" t="inlineStr">
+        <is>
+          <t>1.0, 0.9957446808510638, 0.9914893617021276, 0.9956896551724138, 0.9957081545064378, 1.0, 0.9872881355932204</t>
+        </is>
+      </c>
+      <c r="CQ49" t="n">
+        <v>0.9951314268321804</v>
+      </c>
+      <c r="CR49" t="n">
+        <v>0.9957081545064378</v>
+      </c>
+      <c r="CS49" t="n">
+        <v>0.004195374654362826</v>
+      </c>
+      <c r="CT49" t="n">
+        <v>0.9866491095525175</v>
+      </c>
+      <c r="CU49" t="n">
+        <v>0.9880952380952381</v>
+      </c>
+      <c r="CV49" t="n">
+        <v>0.01138583207389035</v>
+      </c>
+      <c r="CW49" t="inlineStr">
+        <is>
+          <t>1.0, 0.9882352941176471, 0.9764705882352941, 0.9882352941176471, 0.9882352941176471, 1.0, 0.9647058823529412</t>
+        </is>
+      </c>
+      <c r="CX49" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 1.0, 0.9957264957264957, 0.9871794871794872, 0.9914529914529915, 1.0, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CY49" t="n">
+        <v>0.9951159951159951</v>
+      </c>
+      <c r="CZ49" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="DA49" t="n">
+        <v>0.004229672301755485</v>
+      </c>
+      <c r="DB49" t="n">
+        <v>0.9865546218487395</v>
+      </c>
+      <c r="DC49" t="n">
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="DD49" t="n">
+        <v>0.01164403904247985</v>
+      </c>
+      <c r="DE49" t="inlineStr">
+        <is>
+          <t>0.9998982498982499, 0.999798893916541, 0.9994469582704877, 0.9990447461035696, 0.9994469582704877, 1.0, 0.9991452991452991</t>
+        </is>
+      </c>
+      <c r="DF49" t="n">
+        <v>0.9995401579435192</v>
+      </c>
+      <c r="DG49" t="n">
+        <v>0.9994469582704877</v>
+      </c>
+      <c r="DH49" t="n">
+        <v>0.0003433755937094569</v>
       </c>
     </row>
   </sheetData>
